--- a/datasets/subsidy_dataset_updated.xlsx
+++ b/datasets/subsidy_dataset_updated.xlsx
@@ -471,7 +471,7 @@
         <v>2.93</v>
       </c>
       <c r="B2" t="n">
-        <v>6.1541111</v>
+        <v>89.23</v>
       </c>
       <c r="C2" t="n">
         <v>160</v>
@@ -494,7 +494,7 @@
         <v>0.8</v>
       </c>
       <c r="B3" t="n">
-        <v>6.1541111</v>
+        <v>73.09</v>
       </c>
       <c r="C3" t="n">
         <v>100</v>
@@ -517,7 +517,7 @@
         <v>2.77</v>
       </c>
       <c r="B4" t="n">
-        <v>6.1541111</v>
+        <v>94.58</v>
       </c>
       <c r="C4" t="n">
         <v>170</v>
@@ -540,7 +540,7 @@
         <v>1.23</v>
       </c>
       <c r="B5" t="n">
-        <v>6.1541111</v>
+        <v>96.86</v>
       </c>
       <c r="C5" t="n">
         <v>50</v>
@@ -563,7 +563,7 @@
         <v>3.63</v>
       </c>
       <c r="B6" t="n">
-        <v>6.1541111</v>
+        <v>62.16</v>
       </c>
       <c r="C6" t="n">
         <v>180</v>
@@ -586,7 +586,7 @@
         <v>3.53</v>
       </c>
       <c r="B7" t="n">
-        <v>6.1541111</v>
+        <v>69.95</v>
       </c>
       <c r="C7" t="n">
         <v>160</v>
@@ -609,7 +609,7 @@
         <v>2.89</v>
       </c>
       <c r="B8" t="n">
-        <v>6.1541111</v>
+        <v>87.11</v>
       </c>
       <c r="C8" t="n">
         <v>200</v>
@@ -632,7 +632,7 @@
         <v>1.06</v>
       </c>
       <c r="B9" t="n">
-        <v>6.1541111</v>
+        <v>81.78</v>
       </c>
       <c r="C9" t="n">
         <v>153</v>
@@ -655,7 +655,7 @@
         <v>3.31</v>
       </c>
       <c r="B10" t="n">
-        <v>6.1541111</v>
+        <v>85.38000000000001</v>
       </c>
       <c r="C10" t="n">
         <v>123</v>
@@ -678,7 +678,7 @@
         <v>2.77</v>
       </c>
       <c r="B11" t="n">
-        <v>6.1541111</v>
+        <v>75.34</v>
       </c>
       <c r="C11" t="n">
         <v>246</v>
@@ -701,7 +701,7 @@
         <v>0.5</v>
       </c>
       <c r="B12" t="n">
-        <v>6.1541111</v>
+        <v>96.12</v>
       </c>
       <c r="C12" t="n">
         <v>246</v>
@@ -724,7 +724,7 @@
         <v>3.25</v>
       </c>
       <c r="B13" t="n">
-        <v>6.1541111</v>
+        <v>94.91</v>
       </c>
       <c r="C13" t="n">
         <v>450</v>
@@ -747,7 +747,7 @@
         <v>4.15</v>
       </c>
       <c r="B14" t="n">
-        <v>6.1541111</v>
+        <v>86.36</v>
       </c>
       <c r="C14" t="n">
         <v>290</v>
@@ -770,7 +770,7 @@
         <v>3.11</v>
       </c>
       <c r="B15" t="n">
-        <v>6.1541111</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="C15" t="n">
         <v>127</v>
@@ -793,7 +793,7 @@
         <v>3.53</v>
       </c>
       <c r="B16" t="n">
-        <v>6.1541111</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="C16" t="n">
         <v>115</v>
@@ -816,7 +816,7 @@
         <v>2.51</v>
       </c>
       <c r="B17" t="n">
-        <v>6.1541111</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="C17" t="n">
         <v>215.81</v>
@@ -839,7 +839,7 @@
         <v>1.03</v>
       </c>
       <c r="B18" t="n">
-        <v>6.1541111</v>
+        <v>90</v>
       </c>
       <c r="C18" t="n">
         <v>143.32</v>
@@ -862,7 +862,7 @@
         <v>0.68</v>
       </c>
       <c r="B19" t="n">
-        <v>6.1541111</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="C19" t="n">
         <v>178.13</v>
@@ -885,7 +885,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="B20" t="n">
-        <v>6.1541111</v>
+        <v>96.11</v>
       </c>
       <c r="C20" t="n">
         <v>166.51</v>
@@ -908,7 +908,7 @@
         <v>3.02</v>
       </c>
       <c r="B21" t="n">
-        <v>6.1541111</v>
+        <v>84.97</v>
       </c>
       <c r="C21" t="n">
         <v>442.25</v>
@@ -931,7 +931,7 @@
         <v>3.38</v>
       </c>
       <c r="B22" t="n">
-        <v>6.1541111</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="C22" t="n">
         <v>224.52</v>
@@ -954,7 +954,7 @@
         <v>1.18</v>
       </c>
       <c r="B23" t="n">
-        <v>6.1541111</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="C23" t="n">
         <v>227.02</v>
@@ -977,7 +977,7 @@
         <v>2.07</v>
       </c>
       <c r="B24" t="n">
-        <v>6.1541111</v>
+        <v>100.24</v>
       </c>
       <c r="C24" t="n">
         <v>153.42</v>
@@ -1000,7 +1000,7 @@
         <v>1.2</v>
       </c>
       <c r="B25" t="n">
-        <v>6.1541111</v>
+        <v>83.72</v>
       </c>
       <c r="C25" t="n">
         <v>52.44</v>
@@ -1023,7 +1023,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B26" t="n">
-        <v>6.1541111</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="C26" t="n">
         <v>127.54</v>
@@ -1046,7 +1046,7 @@
         <v>5</v>
       </c>
       <c r="B27" t="n">
-        <v>6.1541111</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="C27" t="n">
         <v>196.97</v>
@@ -1069,7 +1069,7 @@
         <v>1.95</v>
       </c>
       <c r="B28" t="n">
-        <v>6.1541111</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="C28" t="n">
         <v>59.03</v>
@@ -1092,7 +1092,7 @@
         <v>1.36</v>
       </c>
       <c r="B29" t="n">
-        <v>6.1541111</v>
+        <v>89.95999999999999</v>
       </c>
       <c r="C29" t="n">
         <v>218.27</v>
@@ -1115,7 +1115,7 @@
         <v>4.99</v>
       </c>
       <c r="B30" t="n">
-        <v>6.1541111</v>
+        <v>90.52</v>
       </c>
       <c r="C30" t="n">
         <v>133.52</v>
@@ -1138,7 +1138,7 @@
         <v>2.16</v>
       </c>
       <c r="B31" t="n">
-        <v>6.1541111</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="C31" t="n">
         <v>100.67</v>
@@ -1161,7 +1161,7 @@
         <v>2.5</v>
       </c>
       <c r="B32" t="n">
-        <v>6.1541111</v>
+        <v>110.01</v>
       </c>
       <c r="C32" t="n">
         <v>451.75</v>
@@ -1184,7 +1184,7 @@
         <v>1.23</v>
       </c>
       <c r="B33" t="n">
-        <v>6.1541111</v>
+        <v>80.69</v>
       </c>
       <c r="C33" t="n">
         <v>121.78</v>
@@ -1207,7 +1207,7 @@
         <v>2.75</v>
       </c>
       <c r="B34" t="n">
-        <v>6.1541111</v>
+        <v>79.42</v>
       </c>
       <c r="C34" t="n">
         <v>157.5</v>
@@ -1230,7 +1230,7 @@
         <v>2.92</v>
       </c>
       <c r="B35" t="n">
-        <v>6.1541111</v>
+        <v>75.81</v>
       </c>
       <c r="C35" t="n">
         <v>179.4</v>
@@ -1253,7 +1253,7 @@
         <v>2.18</v>
       </c>
       <c r="B36" t="n">
-        <v>6.1541111</v>
+        <v>92.95999999999999</v>
       </c>
       <c r="C36" t="n">
         <v>230.5</v>
@@ -1276,7 +1276,7 @@
         <v>4.18</v>
       </c>
       <c r="B37" t="n">
-        <v>6.1541111</v>
+        <v>99.12</v>
       </c>
       <c r="C37" t="n">
         <v>142.08</v>
@@ -1299,7 +1299,7 @@
         <v>2.64</v>
       </c>
       <c r="B38" t="n">
-        <v>6.1541111</v>
+        <v>84.2</v>
       </c>
       <c r="C38" t="n">
         <v>162.94</v>
@@ -1322,7 +1322,7 @@
         <v>3.65</v>
       </c>
       <c r="B39" t="n">
-        <v>6.1541111</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="C39" t="n">
         <v>149.99</v>
@@ -1345,7 +1345,7 @@
         <v>2.24</v>
       </c>
       <c r="B40" t="n">
-        <v>6.1541111</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="C40" t="n">
         <v>305.39</v>
@@ -1368,7 +1368,7 @@
         <v>2.48</v>
       </c>
       <c r="B41" t="n">
-        <v>6.1541111</v>
+        <v>93.38</v>
       </c>
       <c r="C41" t="n">
         <v>121.53</v>
@@ -1391,7 +1391,7 @@
         <v>0.99</v>
       </c>
       <c r="B42" t="n">
-        <v>6.1541111</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="C42" t="n">
         <v>120.81</v>
@@ -1414,7 +1414,7 @@
         <v>1.65</v>
       </c>
       <c r="B43" t="n">
-        <v>6.1541111</v>
+        <v>92.09</v>
       </c>
       <c r="C43" t="n">
         <v>171.82</v>
@@ -1437,7 +1437,7 @@
         <v>1.58</v>
       </c>
       <c r="B44" t="n">
-        <v>6.1541111</v>
+        <v>77.59</v>
       </c>
       <c r="C44" t="n">
         <v>84.06</v>
@@ -1460,7 +1460,7 @@
         <v>2.35</v>
       </c>
       <c r="B45" t="n">
-        <v>6.1541111</v>
+        <v>88.36</v>
       </c>
       <c r="C45" t="n">
         <v>247.54</v>
@@ -1483,7 +1483,7 @@
         <v>2.83</v>
       </c>
       <c r="B46" t="n">
-        <v>6.1541111</v>
+        <v>86.97</v>
       </c>
       <c r="C46" t="n">
         <v>159.2</v>
@@ -1506,7 +1506,7 @@
         <v>1.18</v>
       </c>
       <c r="B47" t="n">
-        <v>6.1541111</v>
+        <v>88.2</v>
       </c>
       <c r="C47" t="n">
         <v>146.98</v>
@@ -1529,7 +1529,7 @@
         <v>2.5</v>
       </c>
       <c r="B48" t="n">
-        <v>6.1541111</v>
+        <v>96.03</v>
       </c>
       <c r="C48" t="n">
         <v>197.77</v>
@@ -1552,7 +1552,7 @@
         <v>2.15</v>
       </c>
       <c r="B49" t="n">
-        <v>6.1541111</v>
+        <v>88.25</v>
       </c>
       <c r="C49" t="n">
         <v>199.15</v>
@@ -1575,7 +1575,7 @@
         <v>3.73</v>
       </c>
       <c r="B50" t="n">
-        <v>6.1541111</v>
+        <v>93.72</v>
       </c>
       <c r="C50" t="n">
         <v>151.15</v>
@@ -1598,7 +1598,7 @@
         <v>1.94</v>
       </c>
       <c r="B51" t="n">
-        <v>6.1541111</v>
+        <v>86.38</v>
       </c>
       <c r="C51" t="n">
         <v>136.92</v>
@@ -1621,7 +1621,7 @@
         <v>1.75</v>
       </c>
       <c r="B52" t="n">
-        <v>6.1541111</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="C52" t="n">
         <v>181.12</v>
@@ -1644,7 +1644,7 @@
         <v>3.69</v>
       </c>
       <c r="B53" t="n">
-        <v>6.1541111</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="C53" t="n">
         <v>150.95</v>
@@ -1667,7 +1667,7 @@
         <v>0.97</v>
       </c>
       <c r="B54" t="n">
-        <v>6.1541111</v>
+        <v>68.09</v>
       </c>
       <c r="C54" t="n">
         <v>175.72</v>
@@ -1690,7 +1690,7 @@
         <v>1.95</v>
       </c>
       <c r="B55" t="n">
-        <v>6.1541111</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="C55" t="n">
         <v>163.16</v>
@@ -1713,7 +1713,7 @@
         <v>3.09</v>
       </c>
       <c r="B56" t="n">
-        <v>6.1541111</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="C56" t="n">
         <v>133.62</v>
@@ -1736,7 +1736,7 @@
         <v>2.48</v>
       </c>
       <c r="B57" t="n">
-        <v>6.1541111</v>
+        <v>77.91</v>
       </c>
       <c r="C57" t="n">
         <v>213.4</v>
@@ -1759,7 +1759,7 @@
         <v>3.21</v>
       </c>
       <c r="B58" t="n">
-        <v>6.1541111</v>
+        <v>82.27</v>
       </c>
       <c r="C58" t="n">
         <v>122.08</v>
@@ -1782,7 +1782,7 @@
         <v>2.15</v>
       </c>
       <c r="B59" t="n">
-        <v>6.1541111</v>
+        <v>103.51</v>
       </c>
       <c r="C59" t="n">
         <v>218.37</v>
@@ -1805,7 +1805,7 @@
         <v>1.68</v>
       </c>
       <c r="B60" t="n">
-        <v>6.1541111</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="C60" t="n">
         <v>149.88</v>
@@ -1828,7 +1828,7 @@
         <v>3.07</v>
       </c>
       <c r="B61" t="n">
-        <v>6.1541111</v>
+        <v>97.19</v>
       </c>
       <c r="C61" t="n">
         <v>146.42</v>
@@ -1851,7 +1851,7 @@
         <v>2.42</v>
       </c>
       <c r="B62" t="n">
-        <v>6.1541111</v>
+        <v>65.38</v>
       </c>
       <c r="C62" t="n">
         <v>124.89</v>
@@ -1874,7 +1874,7 @@
         <v>1.92</v>
       </c>
       <c r="B63" t="n">
-        <v>6.1541111</v>
+        <v>81.55</v>
       </c>
       <c r="C63" t="n">
         <v>129.29</v>
@@ -1897,7 +1897,7 @@
         <v>2.29</v>
       </c>
       <c r="B64" t="n">
-        <v>6.1541111</v>
+        <v>87.52</v>
       </c>
       <c r="C64" t="n">
         <v>220.02</v>
@@ -1920,7 +1920,7 @@
         <v>2.25</v>
       </c>
       <c r="B65" t="n">
-        <v>6.1541111</v>
+        <v>92.61</v>
       </c>
       <c r="C65" t="n">
         <v>231.87</v>
@@ -1943,7 +1943,7 @@
         <v>2.31</v>
       </c>
       <c r="B66" t="n">
-        <v>6.1541111</v>
+        <v>94.11</v>
       </c>
       <c r="C66" t="n">
         <v>177.58</v>
@@ -1966,7 +1966,7 @@
         <v>3.24</v>
       </c>
       <c r="B67" t="n">
-        <v>6.1541111</v>
+        <v>95.09</v>
       </c>
       <c r="C67" t="n">
         <v>178.02</v>
@@ -1989,7 +1989,7 @@
         <v>2.36</v>
       </c>
       <c r="B68" t="n">
-        <v>6.1541111</v>
+        <v>81.39</v>
       </c>
       <c r="C68" t="n">
         <v>265.08</v>
@@ -2012,7 +2012,7 @@
         <v>1.92</v>
       </c>
       <c r="B69" t="n">
-        <v>6.1541111</v>
+        <v>80.02</v>
       </c>
       <c r="C69" t="n">
         <v>252.23</v>
@@ -2035,7 +2035,7 @@
         <v>2.7</v>
       </c>
       <c r="B70" t="n">
-        <v>6.1541111</v>
+        <v>95.87</v>
       </c>
       <c r="C70" t="n">
         <v>160.53</v>
@@ -2058,7 +2058,7 @@
         <v>1</v>
       </c>
       <c r="B71" t="n">
-        <v>6.1541111</v>
+        <v>83.28</v>
       </c>
       <c r="C71" t="n">
         <v>164.75</v>
@@ -2081,7 +2081,7 @@
         <v>3.51</v>
       </c>
       <c r="B72" t="n">
-        <v>6.1541111</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="C72" t="n">
         <v>176.77</v>
@@ -2104,7 +2104,7 @@
         <v>2.88</v>
       </c>
       <c r="B73" t="n">
-        <v>6.1541111</v>
+        <v>71.97</v>
       </c>
       <c r="C73" t="n">
         <v>164.69</v>
@@ -2127,7 +2127,7 @@
         <v>2.71</v>
       </c>
       <c r="B74" t="n">
-        <v>6.1541111</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="C74" t="n">
         <v>54.06</v>
@@ -2150,7 +2150,7 @@
         <v>2.09</v>
       </c>
       <c r="B75" t="n">
-        <v>6.1541111</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="C75" t="n">
         <v>180.37</v>
@@ -2173,7 +2173,7 @@
         <v>3.88</v>
       </c>
       <c r="B76" t="n">
-        <v>6.1541111</v>
+        <v>87.28</v>
       </c>
       <c r="C76" t="n">
         <v>218.43</v>
@@ -2196,7 +2196,7 @@
         <v>2.43</v>
       </c>
       <c r="B77" t="n">
-        <v>6.1541111</v>
+        <v>93.86</v>
       </c>
       <c r="C77" t="n">
         <v>168.46</v>
@@ -2219,7 +2219,7 @@
         <v>2.9</v>
       </c>
       <c r="B78" t="n">
-        <v>6.1541111</v>
+        <v>80.44</v>
       </c>
       <c r="C78" t="n">
         <v>185.23</v>
@@ -2242,7 +2242,7 @@
         <v>3.23</v>
       </c>
       <c r="B79" t="n">
-        <v>6.1541111</v>
+        <v>87.47</v>
       </c>
       <c r="C79" t="n">
         <v>91.44</v>
@@ -2265,7 +2265,7 @@
         <v>2.29</v>
       </c>
       <c r="B80" t="n">
-        <v>6.1541111</v>
+        <v>93.08</v>
       </c>
       <c r="C80" t="n">
         <v>126.09</v>
@@ -2288,7 +2288,7 @@
         <v>1.35</v>
       </c>
       <c r="B81" t="n">
-        <v>6.1541111</v>
+        <v>81.86</v>
       </c>
       <c r="C81" t="n">
         <v>177.6</v>
@@ -2311,7 +2311,7 @@
         <v>2.53</v>
       </c>
       <c r="B82" t="n">
-        <v>6.1541111</v>
+        <v>91.05</v>
       </c>
       <c r="C82" t="n">
         <v>432.59</v>
@@ -2334,7 +2334,7 @@
         <v>3.16</v>
       </c>
       <c r="B83" t="n">
-        <v>6.1541111</v>
+        <v>77.63</v>
       </c>
       <c r="C83" t="n">
         <v>378.67</v>
@@ -2357,7 +2357,7 @@
         <v>1.33</v>
       </c>
       <c r="B84" t="n">
-        <v>6.1541111</v>
+        <v>81.22</v>
       </c>
       <c r="C84" t="n">
         <v>87.2</v>
@@ -2380,7 +2380,7 @@
         <v>0.87</v>
       </c>
       <c r="B85" t="n">
-        <v>6.1541111</v>
+        <v>80.98999999999999</v>
       </c>
       <c r="C85" t="n">
         <v>73.84999999999999</v>
@@ -2403,7 +2403,7 @@
         <v>4.4</v>
       </c>
       <c r="B86" t="n">
-        <v>6.1541111</v>
+        <v>71.22</v>
       </c>
       <c r="C86" t="n">
         <v>49.37</v>
@@ -2426,7 +2426,7 @@
         <v>2.44</v>
       </c>
       <c r="B87" t="n">
-        <v>6.1541111</v>
+        <v>91.42</v>
       </c>
       <c r="C87" t="n">
         <v>80.64</v>
@@ -2449,7 +2449,7 @@
         <v>3.28</v>
       </c>
       <c r="B88" t="n">
-        <v>6.1541111</v>
+        <v>79.94</v>
       </c>
       <c r="C88" t="n">
         <v>127.86</v>
@@ -2472,7 +2472,7 @@
         <v>2.56</v>
       </c>
       <c r="B89" t="n">
-        <v>6.1541111</v>
+        <v>85.72</v>
       </c>
       <c r="C89" t="n">
         <v>86.23999999999999</v>
@@ -2495,7 +2495,7 @@
         <v>0.65</v>
       </c>
       <c r="B90" t="n">
-        <v>6.1541111</v>
+        <v>91.34</v>
       </c>
       <c r="C90" t="n">
         <v>102.61</v>
@@ -2518,7 +2518,7 @@
         <v>1.43</v>
       </c>
       <c r="B91" t="n">
-        <v>6.1541111</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="C91" t="n">
         <v>114.57</v>
@@ -2541,7 +2541,7 @@
         <v>3.43</v>
       </c>
       <c r="B92" t="n">
-        <v>6.1541111</v>
+        <v>93.56</v>
       </c>
       <c r="C92" t="n">
         <v>172.98</v>
@@ -2564,7 +2564,7 @@
         <v>4.01</v>
       </c>
       <c r="B93" t="n">
-        <v>6.1541111</v>
+        <v>84.39</v>
       </c>
       <c r="C93" t="n">
         <v>88.36</v>
@@ -2587,7 +2587,7 @@
         <v>0.5</v>
       </c>
       <c r="B94" t="n">
-        <v>6.1541111</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="C94" t="n">
         <v>215.64</v>
@@ -2610,7 +2610,7 @@
         <v>3.52</v>
       </c>
       <c r="B95" t="n">
-        <v>6.1541111</v>
+        <v>84.62</v>
       </c>
       <c r="C95" t="n">
         <v>215.1</v>
@@ -2633,7 +2633,7 @@
         <v>0.5</v>
       </c>
       <c r="B96" t="n">
-        <v>6.1541111</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="C96" t="n">
         <v>57.84</v>
@@ -2656,7 +2656,7 @@
         <v>1.78</v>
       </c>
       <c r="B97" t="n">
-        <v>6.1541111</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="C97" t="n">
         <v>218.57</v>
@@ -2679,7 +2679,7 @@
         <v>0.5</v>
       </c>
       <c r="B98" t="n">
-        <v>6.1541111</v>
+        <v>69.7</v>
       </c>
       <c r="C98" t="n">
         <v>127.25</v>
@@ -2702,7 +2702,7 @@
         <v>3.44</v>
       </c>
       <c r="B99" t="n">
-        <v>6.1541111</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C99" t="n">
         <v>183.15</v>
@@ -2725,7 +2725,7 @@
         <v>3.25</v>
       </c>
       <c r="B100" t="n">
-        <v>6.1541111</v>
+        <v>90.37</v>
       </c>
       <c r="C100" t="n">
         <v>224.64</v>
@@ -2748,7 +2748,7 @@
         <v>2.46</v>
       </c>
       <c r="B101" t="n">
-        <v>6.1541111</v>
+        <v>74.70999999999999</v>
       </c>
       <c r="C101" t="n">
         <v>131.49</v>
@@ -2771,7 +2771,7 @@
         <v>2.51</v>
       </c>
       <c r="B102" t="n">
-        <v>6.1541111</v>
+        <v>81.03</v>
       </c>
       <c r="C102" t="n">
         <v>167.41</v>
@@ -2794,7 +2794,7 @@
         <v>1.49</v>
       </c>
       <c r="B103" t="n">
-        <v>6.1541111</v>
+        <v>101.16</v>
       </c>
       <c r="C103" t="n">
         <v>456.37</v>
@@ -2817,7 +2817,7 @@
         <v>3.76</v>
       </c>
       <c r="B104" t="n">
-        <v>6.1541111</v>
+        <v>81.3</v>
       </c>
       <c r="C104" t="n">
         <v>56.23</v>
@@ -2840,7 +2840,7 @@
         <v>0.92</v>
       </c>
       <c r="B105" t="n">
-        <v>6.1541111</v>
+        <v>94.42</v>
       </c>
       <c r="C105" t="n">
         <v>52.21</v>
@@ -2863,7 +2863,7 @@
         <v>2.86</v>
       </c>
       <c r="B106" t="n">
-        <v>6.1541111</v>
+        <v>74.37</v>
       </c>
       <c r="C106" t="n">
         <v>59.69</v>
@@ -2886,7 +2886,7 @@
         <v>1.66</v>
       </c>
       <c r="B107" t="n">
-        <v>6.1541111</v>
+        <v>83.11</v>
       </c>
       <c r="C107" t="n">
         <v>93.2</v>
@@ -2909,7 +2909,7 @@
         <v>3.87</v>
       </c>
       <c r="B108" t="n">
-        <v>6.1541111</v>
+        <v>74.17</v>
       </c>
       <c r="C108" t="n">
         <v>106.3</v>
@@ -2932,7 +2932,7 @@
         <v>1.68</v>
       </c>
       <c r="B109" t="n">
-        <v>6.1541111</v>
+        <v>81.5</v>
       </c>
       <c r="C109" t="n">
         <v>148.89</v>
@@ -2955,7 +2955,7 @@
         <v>2.05</v>
       </c>
       <c r="B110" t="n">
-        <v>6.1541111</v>
+        <v>95.66</v>
       </c>
       <c r="C110" t="n">
         <v>216.68</v>
@@ -2978,7 +2978,7 @@
         <v>2.65</v>
       </c>
       <c r="B111" t="n">
-        <v>6.1541111</v>
+        <v>64.84</v>
       </c>
       <c r="C111" t="n">
         <v>467.15</v>
@@ -3001,7 +3001,7 @@
         <v>3.63</v>
       </c>
       <c r="B112" t="n">
-        <v>6.1541111</v>
+        <v>90.78</v>
       </c>
       <c r="C112" t="n">
         <v>164.08</v>
@@ -3024,7 +3024,7 @@
         <v>1.23</v>
       </c>
       <c r="B113" t="n">
-        <v>6.1541111</v>
+        <v>88.42</v>
       </c>
       <c r="C113" t="n">
         <v>114.26</v>
@@ -3047,7 +3047,7 @@
         <v>2.3</v>
       </c>
       <c r="B114" t="n">
-        <v>6.1541111</v>
+        <v>78.44</v>
       </c>
       <c r="C114" t="n">
         <v>47.44</v>
@@ -3070,7 +3070,7 @@
         <v>2.73</v>
       </c>
       <c r="B115" t="n">
-        <v>6.1541111</v>
+        <v>68.22</v>
       </c>
       <c r="C115" t="n">
         <v>54.95</v>
@@ -3093,7 +3093,7 @@
         <v>3.92</v>
       </c>
       <c r="B116" t="n">
-        <v>6.1541111</v>
+        <v>86.44</v>
       </c>
       <c r="C116" t="n">
         <v>120.79</v>
@@ -3116,7 +3116,7 @@
         <v>2.35</v>
       </c>
       <c r="B117" t="n">
-        <v>6.1541111</v>
+        <v>79.22</v>
       </c>
       <c r="C117" t="n">
         <v>99.98999999999999</v>
@@ -3139,7 +3139,7 @@
         <v>3.66</v>
       </c>
       <c r="B118" t="n">
-        <v>6.1541111</v>
+        <v>88.36</v>
       </c>
       <c r="C118" t="n">
         <v>96.89</v>
@@ -3162,7 +3162,7 @@
         <v>1.53</v>
       </c>
       <c r="B119" t="n">
-        <v>6.1541111</v>
+        <v>85.83</v>
       </c>
       <c r="C119" t="n">
         <v>254.78</v>
@@ -3185,7 +3185,7 @@
         <v>1.93</v>
       </c>
       <c r="B120" t="n">
-        <v>6.1541111</v>
+        <v>104.79</v>
       </c>
       <c r="C120" t="n">
         <v>126.2</v>
@@ -3208,7 +3208,7 @@
         <v>2.98</v>
       </c>
       <c r="B121" t="n">
-        <v>6.1541111</v>
+        <v>82.7</v>
       </c>
       <c r="C121" t="n">
         <v>387.2</v>
@@ -3231,7 +3231,7 @@
         <v>0.5</v>
       </c>
       <c r="B122" t="n">
-        <v>6.1541111</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="C122" t="n">
         <v>51.58</v>
@@ -3254,7 +3254,7 @@
         <v>3.08</v>
       </c>
       <c r="B123" t="n">
-        <v>6.1541111</v>
+        <v>87.72</v>
       </c>
       <c r="C123" t="n">
         <v>119.9</v>
@@ -3277,7 +3277,7 @@
         <v>4.25</v>
       </c>
       <c r="B124" t="n">
-        <v>6.1541111</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="C124" t="n">
         <v>63.87</v>
@@ -3300,7 +3300,7 @@
         <v>3.01</v>
       </c>
       <c r="B125" t="n">
-        <v>6.1541111</v>
+        <v>101.88</v>
       </c>
       <c r="C125" t="n">
         <v>355.39</v>
@@ -3323,7 +3323,7 @@
         <v>2.91</v>
       </c>
       <c r="B126" t="n">
-        <v>6.1541111</v>
+        <v>95.59</v>
       </c>
       <c r="C126" t="n">
         <v>168.64</v>
@@ -3346,7 +3346,7 @@
         <v>3.04</v>
       </c>
       <c r="B127" t="n">
-        <v>6.1541111</v>
+        <v>89.84999999999999</v>
       </c>
       <c r="C127" t="n">
         <v>159.7</v>
@@ -3369,7 +3369,7 @@
         <v>2.87</v>
       </c>
       <c r="B128" t="n">
-        <v>6.1541111</v>
+        <v>103.13</v>
       </c>
       <c r="C128" t="n">
         <v>401.75</v>
@@ -3392,7 +3392,7 @@
         <v>3.47</v>
       </c>
       <c r="B129" t="n">
-        <v>6.1541111</v>
+        <v>71.31</v>
       </c>
       <c r="C129" t="n">
         <v>185.26</v>
@@ -3415,7 +3415,7 @@
         <v>3.14</v>
       </c>
       <c r="B130" t="n">
-        <v>6.1541111</v>
+        <v>77.89</v>
       </c>
       <c r="C130" t="n">
         <v>267.14</v>
@@ -3438,7 +3438,7 @@
         <v>2.99</v>
       </c>
       <c r="B131" t="n">
-        <v>6.1541111</v>
+        <v>74.45</v>
       </c>
       <c r="C131" t="n">
         <v>133.96</v>
@@ -3461,7 +3461,7 @@
         <v>3.51</v>
       </c>
       <c r="B132" t="n">
-        <v>6.1541111</v>
+        <v>80.89</v>
       </c>
       <c r="C132" t="n">
         <v>187.66</v>
@@ -3484,7 +3484,7 @@
         <v>3.33</v>
       </c>
       <c r="B133" t="n">
-        <v>6.1541111</v>
+        <v>69.05</v>
       </c>
       <c r="C133" t="n">
         <v>100.67</v>
@@ -3507,7 +3507,7 @@
         <v>3.69</v>
       </c>
       <c r="B134" t="n">
-        <v>6.1541111</v>
+        <v>93.19</v>
       </c>
       <c r="C134" t="n">
         <v>201.48</v>
@@ -3530,7 +3530,7 @@
         <v>1.58</v>
       </c>
       <c r="B135" t="n">
-        <v>6.1541111</v>
+        <v>82.91</v>
       </c>
       <c r="C135" t="n">
         <v>196.74</v>
@@ -3553,7 +3553,7 @@
         <v>3</v>
       </c>
       <c r="B136" t="n">
-        <v>6.1541111</v>
+        <v>67.92</v>
       </c>
       <c r="C136" t="n">
         <v>178.93</v>
@@ -3576,7 +3576,7 @@
         <v>0.7</v>
       </c>
       <c r="B137" t="n">
-        <v>6.1541111</v>
+        <v>73.38</v>
       </c>
       <c r="C137" t="n">
         <v>140.76</v>
@@ -3599,7 +3599,7 @@
         <v>2.69</v>
       </c>
       <c r="B138" t="n">
-        <v>6.1541111</v>
+        <v>89.33</v>
       </c>
       <c r="C138" t="n">
         <v>242.5</v>
@@ -3622,7 +3622,7 @@
         <v>0.82</v>
       </c>
       <c r="B139" t="n">
-        <v>6.1541111</v>
+        <v>95.63</v>
       </c>
       <c r="C139" t="n">
         <v>260.51</v>
@@ -3645,7 +3645,7 @@
         <v>0.5</v>
       </c>
       <c r="B140" t="n">
-        <v>6.1541111</v>
+        <v>109.53</v>
       </c>
       <c r="C140" t="n">
         <v>55.33</v>
@@ -3668,7 +3668,7 @@
         <v>4.11</v>
       </c>
       <c r="B141" t="n">
-        <v>6.1541111</v>
+        <v>110.01</v>
       </c>
       <c r="C141" t="n">
         <v>162.55</v>
@@ -3691,7 +3691,7 @@
         <v>2.38</v>
       </c>
       <c r="B142" t="n">
-        <v>6.1541111</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="C142" t="n">
         <v>323.15</v>
@@ -3714,7 +3714,7 @@
         <v>1.34</v>
       </c>
       <c r="B143" t="n">
-        <v>6.1541111</v>
+        <v>73.7</v>
       </c>
       <c r="C143" t="n">
         <v>139.5</v>
@@ -3737,7 +3737,7 @@
         <v>1.74</v>
       </c>
       <c r="B144" t="n">
-        <v>6.1541111</v>
+        <v>60.37</v>
       </c>
       <c r="C144" t="n">
         <v>169.7</v>
@@ -3760,7 +3760,7 @@
         <v>3.3</v>
       </c>
       <c r="B145" t="n">
-        <v>6.1541111</v>
+        <v>88.78</v>
       </c>
       <c r="C145" t="n">
         <v>416.98</v>
@@ -3783,7 +3783,7 @@
         <v>4.57</v>
       </c>
       <c r="B146" t="n">
-        <v>6.1541111</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="C146" t="n">
         <v>178.67</v>
@@ -3806,7 +3806,7 @@
         <v>0.5</v>
       </c>
       <c r="B147" t="n">
-        <v>6.1541111</v>
+        <v>80.59</v>
       </c>
       <c r="C147" t="n">
         <v>115.49</v>
@@ -3829,7 +3829,7 @@
         <v>1.41</v>
       </c>
       <c r="B148" t="n">
-        <v>6.1541111</v>
+        <v>78.23</v>
       </c>
       <c r="C148" t="n">
         <v>48.66</v>
@@ -3852,7 +3852,7 @@
         <v>2.6</v>
       </c>
       <c r="B149" t="n">
-        <v>6.1541111</v>
+        <v>83.88</v>
       </c>
       <c r="C149" t="n">
         <v>284.68</v>
@@ -3875,7 +3875,7 @@
         <v>2.36</v>
       </c>
       <c r="B150" t="n">
-        <v>6.1541111</v>
+        <v>98.36</v>
       </c>
       <c r="C150" t="n">
         <v>86.06999999999999</v>
@@ -3898,7 +3898,7 @@
         <v>2</v>
       </c>
       <c r="B151" t="n">
-        <v>6.1541111</v>
+        <v>87.45999999999999</v>
       </c>
       <c r="C151" t="n">
         <v>154.93</v>
@@ -3921,7 +3921,7 @@
         <v>4.44</v>
       </c>
       <c r="B152" t="n">
-        <v>6.1541111</v>
+        <v>83.67</v>
       </c>
       <c r="C152" t="n">
         <v>109.29</v>
@@ -3944,7 +3944,7 @@
         <v>1.83</v>
       </c>
       <c r="B153" t="n">
-        <v>6.1541111</v>
+        <v>73.14</v>
       </c>
       <c r="C153" t="n">
         <v>219.04</v>
@@ -3967,7 +3967,7 @@
         <v>2.27</v>
       </c>
       <c r="B154" t="n">
-        <v>6.1541111</v>
+        <v>65.48</v>
       </c>
       <c r="C154" t="n">
         <v>88.22</v>
@@ -3990,7 +3990,7 @@
         <v>3.45</v>
       </c>
       <c r="B155" t="n">
-        <v>6.1541111</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="C155" t="n">
         <v>179.27</v>
@@ -4013,7 +4013,7 @@
         <v>3.3</v>
       </c>
       <c r="B156" t="n">
-        <v>6.1541111</v>
+        <v>84.93000000000001</v>
       </c>
       <c r="C156" t="n">
         <v>116.56</v>
@@ -4036,7 +4036,7 @@
         <v>1.56</v>
       </c>
       <c r="B157" t="n">
-        <v>6.1541111</v>
+        <v>106.79</v>
       </c>
       <c r="C157" t="n">
         <v>54.67</v>
@@ -4059,7 +4059,7 @@
         <v>3.27</v>
       </c>
       <c r="B158" t="n">
-        <v>6.1541111</v>
+        <v>87.14</v>
       </c>
       <c r="C158" t="n">
         <v>132.61</v>
@@ -4082,7 +4082,7 @@
         <v>2.73</v>
       </c>
       <c r="B159" t="n">
-        <v>6.1541111</v>
+        <v>97.36</v>
       </c>
       <c r="C159" t="n">
         <v>289.61</v>
@@ -4105,7 +4105,7 @@
         <v>1.98</v>
       </c>
       <c r="B160" t="n">
-        <v>6.1541111</v>
+        <v>79.58</v>
       </c>
       <c r="C160" t="n">
         <v>191.92</v>
@@ -4128,7 +4128,7 @@
         <v>1.38</v>
       </c>
       <c r="B161" t="n">
-        <v>6.1541111</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="C161" t="n">
         <v>257.72</v>
@@ -4151,7 +4151,7 @@
         <v>0.89</v>
       </c>
       <c r="B162" t="n">
-        <v>6.1541111</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="C162" t="n">
         <v>241.78</v>
@@ -4174,7 +4174,7 @@
         <v>3.36</v>
       </c>
       <c r="B163" t="n">
-        <v>6.1541111</v>
+        <v>76.87</v>
       </c>
       <c r="C163" t="n">
         <v>162.54</v>
@@ -4197,7 +4197,7 @@
         <v>1.97</v>
       </c>
       <c r="B164" t="n">
-        <v>6.1541111</v>
+        <v>110.01</v>
       </c>
       <c r="C164" t="n">
         <v>124.15</v>
@@ -4220,7 +4220,7 @@
         <v>4.01</v>
       </c>
       <c r="B165" t="n">
-        <v>6.1541111</v>
+        <v>75.72</v>
       </c>
       <c r="C165" t="n">
         <v>93.43000000000001</v>
@@ -4243,7 +4243,7 @@
         <v>3.77</v>
       </c>
       <c r="B166" t="n">
-        <v>6.1541111</v>
+        <v>95.63</v>
       </c>
       <c r="C166" t="n">
         <v>166.93</v>
@@ -4266,7 +4266,7 @@
         <v>4.22</v>
       </c>
       <c r="B167" t="n">
-        <v>6.1541111</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="C167" t="n">
         <v>244.45</v>
@@ -4289,7 +4289,7 @@
         <v>3.61</v>
       </c>
       <c r="B168" t="n">
-        <v>6.1541111</v>
+        <v>96.75</v>
       </c>
       <c r="C168" t="n">
         <v>97</v>
@@ -4312,7 +4312,7 @@
         <v>1.05</v>
       </c>
       <c r="B169" t="n">
-        <v>6.1541111</v>
+        <v>90.19</v>
       </c>
       <c r="C169" t="n">
         <v>190.22</v>
@@ -4335,7 +4335,7 @@
         <v>3.42</v>
       </c>
       <c r="B170" t="n">
-        <v>6.1541111</v>
+        <v>83.69</v>
       </c>
       <c r="C170" t="n">
         <v>105.77</v>
@@ -4358,7 +4358,7 @@
         <v>3.71</v>
       </c>
       <c r="B171" t="n">
-        <v>6.1541111</v>
+        <v>85.09</v>
       </c>
       <c r="C171" t="n">
         <v>200.32</v>
@@ -4381,7 +4381,7 @@
         <v>3.01</v>
       </c>
       <c r="B172" t="n">
-        <v>6.1541111</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="C172" t="n">
         <v>97.72</v>
@@ -4404,7 +4404,7 @@
         <v>0.5</v>
       </c>
       <c r="B173" t="n">
-        <v>6.1541111</v>
+        <v>90.92</v>
       </c>
       <c r="C173" t="n">
         <v>255.64</v>
@@ -4427,7 +4427,7 @@
         <v>4.12</v>
       </c>
       <c r="B174" t="n">
-        <v>6.1541111</v>
+        <v>80.11</v>
       </c>
       <c r="C174" t="n">
         <v>217.41</v>
@@ -4450,7 +4450,7 @@
         <v>2.21</v>
       </c>
       <c r="B175" t="n">
-        <v>6.1541111</v>
+        <v>70.86</v>
       </c>
       <c r="C175" t="n">
         <v>259.41</v>
@@ -4473,7 +4473,7 @@
         <v>0.59</v>
       </c>
       <c r="B176" t="n">
-        <v>6.1541111</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="C176" t="n">
         <v>186.92</v>
@@ -4496,7 +4496,7 @@
         <v>2.49</v>
       </c>
       <c r="B177" t="n">
-        <v>6.1541111</v>
+        <v>87.64</v>
       </c>
       <c r="C177" t="n">
         <v>101.78</v>
@@ -4519,7 +4519,7 @@
         <v>4.54</v>
       </c>
       <c r="B178" t="n">
-        <v>6.1541111</v>
+        <v>104.52</v>
       </c>
       <c r="C178" t="n">
         <v>42.14</v>
@@ -4542,7 +4542,7 @@
         <v>2.21</v>
       </c>
       <c r="B179" t="n">
-        <v>6.1541111</v>
+        <v>87.48999999999999</v>
       </c>
       <c r="C179" t="n">
         <v>197.69</v>
@@ -4565,7 +4565,7 @@
         <v>1.68</v>
       </c>
       <c r="B180" t="n">
-        <v>6.1541111</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="C180" t="n">
         <v>121.71</v>
@@ -4588,7 +4588,7 @@
         <v>2.39</v>
       </c>
       <c r="B181" t="n">
-        <v>6.1541111</v>
+        <v>89</v>
       </c>
       <c r="C181" t="n">
         <v>102.02</v>
@@ -4611,7 +4611,7 @@
         <v>4.28</v>
       </c>
       <c r="B182" t="n">
-        <v>6.1541111</v>
+        <v>101.24</v>
       </c>
       <c r="C182" t="n">
         <v>90.41</v>
@@ -4634,7 +4634,7 @@
         <v>2.1</v>
       </c>
       <c r="B183" t="n">
-        <v>6.1541111</v>
+        <v>88.2</v>
       </c>
       <c r="C183" t="n">
         <v>151.02</v>
@@ -4657,7 +4657,7 @@
         <v>2.38</v>
       </c>
       <c r="B184" t="n">
-        <v>6.1541111</v>
+        <v>80.64</v>
       </c>
       <c r="C184" t="n">
         <v>107.23</v>
@@ -4680,7 +4680,7 @@
         <v>2.3</v>
       </c>
       <c r="B185" t="n">
-        <v>6.1541111</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="C185" t="n">
         <v>247.88</v>
@@ -4703,7 +4703,7 @@
         <v>1.15</v>
       </c>
       <c r="B186" t="n">
-        <v>6.1541111</v>
+        <v>90.72</v>
       </c>
       <c r="C186" t="n">
         <v>237.98</v>
@@ -4726,7 +4726,7 @@
         <v>2.71</v>
       </c>
       <c r="B187" t="n">
-        <v>6.1541111</v>
+        <v>104</v>
       </c>
       <c r="C187" t="n">
         <v>442.72</v>
@@ -4749,7 +4749,7 @@
         <v>1.9</v>
       </c>
       <c r="B188" t="n">
-        <v>6.1541111</v>
+        <v>87.77</v>
       </c>
       <c r="C188" t="n">
         <v>225.61</v>
@@ -4772,7 +4772,7 @@
         <v>1.49</v>
       </c>
       <c r="B189" t="n">
-        <v>6.1541111</v>
+        <v>70.88</v>
       </c>
       <c r="C189" t="n">
         <v>150.44</v>
@@ -4795,7 +4795,7 @@
         <v>1.83</v>
       </c>
       <c r="B190" t="n">
-        <v>6.1541111</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="C190" t="n">
         <v>106.51</v>
@@ -4818,7 +4818,7 @@
         <v>2.24</v>
       </c>
       <c r="B191" t="n">
-        <v>6.1541111</v>
+        <v>105.38</v>
       </c>
       <c r="C191" t="n">
         <v>125.26</v>
@@ -4841,7 +4841,7 @@
         <v>2.03</v>
       </c>
       <c r="B192" t="n">
-        <v>6.1541111</v>
+        <v>106.26</v>
       </c>
       <c r="C192" t="n">
         <v>414.25</v>
@@ -4864,7 +4864,7 @@
         <v>2.51</v>
       </c>
       <c r="B193" t="n">
-        <v>6.1541111</v>
+        <v>83.42</v>
       </c>
       <c r="C193" t="n">
         <v>150.97</v>
@@ -4887,7 +4887,7 @@
         <v>1.14</v>
       </c>
       <c r="B194" t="n">
-        <v>6.1541111</v>
+        <v>80.97</v>
       </c>
       <c r="C194" t="n">
         <v>225.55</v>
@@ -4910,7 +4910,7 @@
         <v>1.48</v>
       </c>
       <c r="B195" t="n">
-        <v>6.1541111</v>
+        <v>103.11</v>
       </c>
       <c r="C195" t="n">
         <v>167.55</v>
@@ -4933,7 +4933,7 @@
         <v>3.71</v>
       </c>
       <c r="B196" t="n">
-        <v>6.1541111</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="C196" t="n">
         <v>155.9</v>
@@ -4956,7 +4956,7 @@
         <v>4.37</v>
       </c>
       <c r="B197" t="n">
-        <v>6.1541111</v>
+        <v>74.84</v>
       </c>
       <c r="C197" t="n">
         <v>144.58</v>
@@ -4979,7 +4979,7 @@
         <v>1.81</v>
       </c>
       <c r="B198" t="n">
-        <v>6.1541111</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="C198" t="n">
         <v>94.11</v>
@@ -5002,7 +5002,7 @@
         <v>0.8</v>
       </c>
       <c r="B199" t="n">
-        <v>6.1541111</v>
+        <v>80.84</v>
       </c>
       <c r="C199" t="n">
         <v>234.06</v>
@@ -5025,7 +5025,7 @@
         <v>0.5</v>
       </c>
       <c r="B200" t="n">
-        <v>6.1541111</v>
+        <v>85.51000000000001</v>
       </c>
       <c r="C200" t="n">
         <v>60.86</v>
@@ -5048,7 +5048,7 @@
         <v>2.89</v>
       </c>
       <c r="B201" t="n">
-        <v>6.1541111</v>
+        <v>83.61</v>
       </c>
       <c r="C201" t="n">
         <v>188.32</v>
@@ -5071,7 +5071,7 @@
         <v>2.43</v>
       </c>
       <c r="B202" t="n">
-        <v>6.1541111</v>
+        <v>89.62</v>
       </c>
       <c r="C202" t="n">
         <v>385.63</v>
@@ -5094,7 +5094,7 @@
         <v>0.97</v>
       </c>
       <c r="B203" t="n">
-        <v>6.1541111</v>
+        <v>102.46</v>
       </c>
       <c r="C203" t="n">
         <v>175.83</v>
@@ -5117,7 +5117,7 @@
         <v>2.04</v>
       </c>
       <c r="B204" t="n">
-        <v>6.1541111</v>
+        <v>86.66</v>
       </c>
       <c r="C204" t="n">
         <v>115.36</v>
@@ -5140,7 +5140,7 @@
         <v>1.22</v>
       </c>
       <c r="B205" t="n">
-        <v>6.1541111</v>
+        <v>93.3</v>
       </c>
       <c r="C205" t="n">
         <v>423.91</v>
@@ -5163,7 +5163,7 @@
         <v>2.82</v>
       </c>
       <c r="B206" t="n">
-        <v>6.1541111</v>
+        <v>60.97</v>
       </c>
       <c r="C206" t="n">
         <v>89.01000000000001</v>
@@ -5186,7 +5186,7 @@
         <v>1.15</v>
       </c>
       <c r="B207" t="n">
-        <v>6.1541111</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="C207" t="n">
         <v>40</v>
@@ -5209,7 +5209,7 @@
         <v>3.42</v>
       </c>
       <c r="B208" t="n">
-        <v>6.1541111</v>
+        <v>75.45</v>
       </c>
       <c r="C208" t="n">
         <v>381.79</v>
@@ -5232,7 +5232,7 @@
         <v>2.27</v>
       </c>
       <c r="B209" t="n">
-        <v>6.1541111</v>
+        <v>70.95</v>
       </c>
       <c r="C209" t="n">
         <v>79.94</v>
@@ -5255,7 +5255,7 @@
         <v>2.23</v>
       </c>
       <c r="B210" t="n">
-        <v>6.1541111</v>
+        <v>75.03</v>
       </c>
       <c r="C210" t="n">
         <v>92.04000000000001</v>
@@ -5278,7 +5278,7 @@
         <v>1.99</v>
       </c>
       <c r="B211" t="n">
-        <v>6.1541111</v>
+        <v>81.56</v>
       </c>
       <c r="C211" t="n">
         <v>52.04</v>
@@ -5301,7 +5301,7 @@
         <v>2.12</v>
       </c>
       <c r="B212" t="n">
-        <v>6.1541111</v>
+        <v>96.56</v>
       </c>
       <c r="C212" t="n">
         <v>44.45</v>
@@ -5324,7 +5324,7 @@
         <v>1.33</v>
       </c>
       <c r="B213" t="n">
-        <v>6.1541111</v>
+        <v>69.66</v>
       </c>
       <c r="C213" t="n">
         <v>79.52</v>
@@ -5347,7 +5347,7 @@
         <v>1.13</v>
       </c>
       <c r="B214" t="n">
-        <v>6.1541111</v>
+        <v>85.94</v>
       </c>
       <c r="C214" t="n">
         <v>144.98</v>
@@ -5370,7 +5370,7 @@
         <v>3.7</v>
       </c>
       <c r="B215" t="n">
-        <v>6.1541111</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="C215" t="n">
         <v>185</v>
@@ -5393,7 +5393,7 @@
         <v>2.25</v>
       </c>
       <c r="B216" t="n">
-        <v>6.1541111</v>
+        <v>81.64</v>
       </c>
       <c r="C216" t="n">
         <v>128.67</v>
@@ -5416,7 +5416,7 @@
         <v>2.67</v>
       </c>
       <c r="B217" t="n">
-        <v>6.1541111</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="C217" t="n">
         <v>157.33</v>
@@ -5439,7 +5439,7 @@
         <v>4.08</v>
       </c>
       <c r="B218" t="n">
-        <v>6.1541111</v>
+        <v>92.03</v>
       </c>
       <c r="C218" t="n">
         <v>144.74</v>
@@ -5462,7 +5462,7 @@
         <v>3.61</v>
       </c>
       <c r="B219" t="n">
-        <v>6.1541111</v>
+        <v>101.62</v>
       </c>
       <c r="C219" t="n">
         <v>111.32</v>
@@ -5485,7 +5485,7 @@
         <v>2.94</v>
       </c>
       <c r="B220" t="n">
-        <v>6.1541111</v>
+        <v>83.72</v>
       </c>
       <c r="C220" t="n">
         <v>225.44</v>
@@ -5508,7 +5508,7 @@
         <v>2.79</v>
       </c>
       <c r="B221" t="n">
-        <v>6.1541111</v>
+        <v>77.22</v>
       </c>
       <c r="C221" t="n">
         <v>65.84999999999999</v>
@@ -5531,7 +5531,7 @@
         <v>0.5</v>
       </c>
       <c r="B222" t="n">
-        <v>6.1541111</v>
+        <v>82.89</v>
       </c>
       <c r="C222" t="n">
         <v>71.01000000000001</v>
@@ -5554,7 +5554,7 @@
         <v>2.49</v>
       </c>
       <c r="B223" t="n">
-        <v>6.1541111</v>
+        <v>88.48</v>
       </c>
       <c r="C223" t="n">
         <v>50.43</v>
@@ -5577,7 +5577,7 @@
         <v>2.04</v>
       </c>
       <c r="B224" t="n">
-        <v>6.1541111</v>
+        <v>87.69</v>
       </c>
       <c r="C224" t="n">
         <v>178.44</v>
@@ -5600,7 +5600,7 @@
         <v>2.09</v>
       </c>
       <c r="B225" t="n">
-        <v>6.1541111</v>
+        <v>72.56</v>
       </c>
       <c r="C225" t="n">
         <v>227.61</v>
@@ -5623,7 +5623,7 @@
         <v>0.5</v>
       </c>
       <c r="B226" t="n">
-        <v>6.1541111</v>
+        <v>86.66</v>
       </c>
       <c r="C226" t="n">
         <v>242.02</v>
@@ -5646,7 +5646,7 @@
         <v>2.35</v>
       </c>
       <c r="B227" t="n">
-        <v>6.1541111</v>
+        <v>88.31</v>
       </c>
       <c r="C227" t="n">
         <v>245.98</v>
@@ -5669,7 +5669,7 @@
         <v>2.44</v>
       </c>
       <c r="B228" t="n">
-        <v>6.1541111</v>
+        <v>110.01</v>
       </c>
       <c r="C228" t="n">
         <v>157.12</v>
@@ -5692,7 +5692,7 @@
         <v>1.2</v>
       </c>
       <c r="B229" t="n">
-        <v>6.1541111</v>
+        <v>108.09</v>
       </c>
       <c r="C229" t="n">
         <v>113.22</v>
@@ -5715,7 +5715,7 @@
         <v>2.22</v>
       </c>
       <c r="B230" t="n">
-        <v>6.1541111</v>
+        <v>75.33</v>
       </c>
       <c r="C230" t="n">
         <v>187.01</v>
@@ -5738,7 +5738,7 @@
         <v>2.14</v>
       </c>
       <c r="B231" t="n">
-        <v>6.1541111</v>
+        <v>82.12</v>
       </c>
       <c r="C231" t="n">
         <v>151.35</v>
@@ -5761,7 +5761,7 @@
         <v>3.28</v>
       </c>
       <c r="B232" t="n">
-        <v>6.1541111</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="C232" t="n">
         <v>180.8</v>
@@ -5784,7 +5784,7 @@
         <v>2.09</v>
       </c>
       <c r="B233" t="n">
-        <v>6.1541111</v>
+        <v>78.48</v>
       </c>
       <c r="C233" t="n">
         <v>243.02</v>
@@ -5807,7 +5807,7 @@
         <v>2.33</v>
       </c>
       <c r="B234" t="n">
-        <v>6.1541111</v>
+        <v>89.36</v>
       </c>
       <c r="C234" t="n">
         <v>232.6</v>
@@ -5830,7 +5830,7 @@
         <v>3.24</v>
       </c>
       <c r="B235" t="n">
-        <v>6.1541111</v>
+        <v>100.04</v>
       </c>
       <c r="C235" t="n">
         <v>149.47</v>
@@ -5853,7 +5853,7 @@
         <v>1.15</v>
       </c>
       <c r="B236" t="n">
-        <v>6.1541111</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="C236" t="n">
         <v>135.72</v>
@@ -5876,7 +5876,7 @@
         <v>3.38</v>
       </c>
       <c r="B237" t="n">
-        <v>6.1541111</v>
+        <v>77.72</v>
       </c>
       <c r="C237" t="n">
         <v>128.86</v>
@@ -5899,7 +5899,7 @@
         <v>1.78</v>
       </c>
       <c r="B238" t="n">
-        <v>6.1541111</v>
+        <v>60.37</v>
       </c>
       <c r="C238" t="n">
         <v>114.29</v>
@@ -5922,7 +5922,7 @@
         <v>1.84</v>
       </c>
       <c r="B239" t="n">
-        <v>6.1541111</v>
+        <v>83.62</v>
       </c>
       <c r="C239" t="n">
         <v>184.5</v>
@@ -5945,7 +5945,7 @@
         <v>1.86</v>
       </c>
       <c r="B240" t="n">
-        <v>6.1541111</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="C240" t="n">
         <v>162.13</v>
@@ -5968,7 +5968,7 @@
         <v>1.83</v>
       </c>
       <c r="B241" t="n">
-        <v>6.1541111</v>
+        <v>79.22</v>
       </c>
       <c r="C241" t="n">
         <v>94.25</v>
@@ -5991,7 +5991,7 @@
         <v>3.86</v>
       </c>
       <c r="B242" t="n">
-        <v>6.1541111</v>
+        <v>75.05</v>
       </c>
       <c r="C242" t="n">
         <v>110.28</v>
@@ -6014,7 +6014,7 @@
         <v>0.5</v>
       </c>
       <c r="B243" t="n">
-        <v>6.1541111</v>
+        <v>84.44</v>
       </c>
       <c r="C243" t="n">
         <v>206.61</v>
@@ -6037,7 +6037,7 @@
         <v>2.84</v>
       </c>
       <c r="B244" t="n">
-        <v>6.1541111</v>
+        <v>64.48</v>
       </c>
       <c r="C244" t="n">
         <v>301.69</v>
@@ -6060,7 +6060,7 @@
         <v>3.54</v>
       </c>
       <c r="B245" t="n">
-        <v>6.1541111</v>
+        <v>67.97</v>
       </c>
       <c r="C245" t="n">
         <v>106.68</v>
@@ -6083,7 +6083,7 @@
         <v>5</v>
       </c>
       <c r="B246" t="n">
-        <v>6.1541111</v>
+        <v>110.01</v>
       </c>
       <c r="C246" t="n">
         <v>100.66</v>
@@ -6106,7 +6106,7 @@
         <v>4.33</v>
       </c>
       <c r="B247" t="n">
-        <v>6.1541111</v>
+        <v>70.12</v>
       </c>
       <c r="C247" t="n">
         <v>224.46</v>
@@ -6129,7 +6129,7 @@
         <v>2.84</v>
       </c>
       <c r="B248" t="n">
-        <v>6.1541111</v>
+        <v>72.41</v>
       </c>
       <c r="C248" t="n">
         <v>107.11</v>
@@ -6152,7 +6152,7 @@
         <v>1.27</v>
       </c>
       <c r="B249" t="n">
-        <v>6.1541111</v>
+        <v>107.61</v>
       </c>
       <c r="C249" t="n">
         <v>148.1</v>
@@ -6175,7 +6175,7 @@
         <v>0.5</v>
       </c>
       <c r="B250" t="n">
-        <v>6.1541111</v>
+        <v>110.01</v>
       </c>
       <c r="C250" t="n">
         <v>397.12</v>
@@ -6198,7 +6198,7 @@
         <v>3.62</v>
       </c>
       <c r="B251" t="n">
-        <v>6.1541111</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="C251" t="n">
         <v>89.88</v>
@@ -6221,7 +6221,7 @@
         <v>1.16</v>
       </c>
       <c r="B252" t="n">
-        <v>6.1541111</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="C252" t="n">
         <v>148.54</v>
@@ -6244,7 +6244,7 @@
         <v>2.58</v>
       </c>
       <c r="B253" t="n">
-        <v>6.1541111</v>
+        <v>89.67</v>
       </c>
       <c r="C253" t="n">
         <v>97.41</v>
@@ -6267,7 +6267,7 @@
         <v>3.93</v>
       </c>
       <c r="B254" t="n">
-        <v>6.1541111</v>
+        <v>106.32</v>
       </c>
       <c r="C254" t="n">
         <v>288.17</v>
@@ -6290,7 +6290,7 @@
         <v>1.63</v>
       </c>
       <c r="B255" t="n">
-        <v>6.1541111</v>
+        <v>73.73</v>
       </c>
       <c r="C255" t="n">
         <v>127.42</v>
@@ -6313,7 +6313,7 @@
         <v>2.08</v>
       </c>
       <c r="B256" t="n">
-        <v>6.1541111</v>
+        <v>82.63</v>
       </c>
       <c r="C256" t="n">
         <v>247.11</v>
@@ -6336,7 +6336,7 @@
         <v>5</v>
       </c>
       <c r="B257" t="n">
-        <v>6.1541111</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="C257" t="n">
         <v>87.12</v>
@@ -6359,7 +6359,7 @@
         <v>0.59</v>
       </c>
       <c r="B258" t="n">
-        <v>6.1541111</v>
+        <v>90.79000000000001</v>
       </c>
       <c r="C258" t="n">
         <v>144.32</v>
@@ -6382,7 +6382,7 @@
         <v>0.91</v>
       </c>
       <c r="B259" t="n">
-        <v>6.1541111</v>
+        <v>81.06</v>
       </c>
       <c r="C259" t="n">
         <v>168.84</v>
@@ -6405,7 +6405,7 @@
         <v>2.19</v>
       </c>
       <c r="B260" t="n">
-        <v>6.1541111</v>
+        <v>83.97</v>
       </c>
       <c r="C260" t="n">
         <v>243.12</v>
@@ -6428,7 +6428,7 @@
         <v>2.01</v>
       </c>
       <c r="B261" t="n">
-        <v>6.1541111</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="C261" t="n">
         <v>288.59</v>
@@ -6451,7 +6451,7 @@
         <v>0.73</v>
       </c>
       <c r="B262" t="n">
-        <v>6.1541111</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="C262" t="n">
         <v>178.28</v>
@@ -6474,7 +6474,7 @@
         <v>2.39</v>
       </c>
       <c r="B263" t="n">
-        <v>6.1541111</v>
+        <v>82.38</v>
       </c>
       <c r="C263" t="n">
         <v>246.96</v>
@@ -6497,7 +6497,7 @@
         <v>1.79</v>
       </c>
       <c r="B264" t="n">
-        <v>6.1541111</v>
+        <v>88.36</v>
       </c>
       <c r="C264" t="n">
         <v>184.76</v>
@@ -6520,7 +6520,7 @@
         <v>0.85</v>
       </c>
       <c r="B265" t="n">
-        <v>6.1541111</v>
+        <v>78.91</v>
       </c>
       <c r="C265" t="n">
         <v>118.62</v>
@@ -6543,7 +6543,7 @@
         <v>0.71</v>
       </c>
       <c r="B266" t="n">
-        <v>6.1541111</v>
+        <v>91.23</v>
       </c>
       <c r="C266" t="n">
         <v>99.67</v>
@@ -6566,7 +6566,7 @@
         <v>2.98</v>
       </c>
       <c r="B267" t="n">
-        <v>6.1541111</v>
+        <v>97.72</v>
       </c>
       <c r="C267" t="n">
         <v>86.89</v>
@@ -6589,7 +6589,7 @@
         <v>0.5</v>
       </c>
       <c r="B268" t="n">
-        <v>6.1541111</v>
+        <v>87.44</v>
       </c>
       <c r="C268" t="n">
         <v>153.52</v>
@@ -6612,7 +6612,7 @@
         <v>1.28</v>
       </c>
       <c r="B269" t="n">
-        <v>6.1541111</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="C269" t="n">
         <v>121.44</v>
@@ -6635,7 +6635,7 @@
         <v>3.12</v>
       </c>
       <c r="B270" t="n">
-        <v>6.1541111</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="C270" t="n">
         <v>193.67</v>
@@ -6658,7 +6658,7 @@
         <v>0.5</v>
       </c>
       <c r="B271" t="n">
-        <v>6.1541111</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="C271" t="n">
         <v>86.88</v>
@@ -6681,7 +6681,7 @@
         <v>4.74</v>
       </c>
       <c r="B272" t="n">
-        <v>6.1541111</v>
+        <v>76.91</v>
       </c>
       <c r="C272" t="n">
         <v>130.18</v>
@@ -6704,7 +6704,7 @@
         <v>0.66</v>
       </c>
       <c r="B273" t="n">
-        <v>6.1541111</v>
+        <v>89.37</v>
       </c>
       <c r="C273" t="n">
         <v>138.97</v>
@@ -6727,7 +6727,7 @@
         <v>3.21</v>
       </c>
       <c r="B274" t="n">
-        <v>6.1541111</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="C274" t="n">
         <v>192.14</v>
@@ -6750,7 +6750,7 @@
         <v>3.95</v>
       </c>
       <c r="B275" t="n">
-        <v>6.1541111</v>
+        <v>110.01</v>
       </c>
       <c r="C275" t="n">
         <v>470</v>
@@ -6773,7 +6773,7 @@
         <v>2.61</v>
       </c>
       <c r="B276" t="n">
-        <v>6.1541111</v>
+        <v>104.45</v>
       </c>
       <c r="C276" t="n">
         <v>139.69</v>
@@ -6796,7 +6796,7 @@
         <v>2.36</v>
       </c>
       <c r="B277" t="n">
-        <v>6.1541111</v>
+        <v>90.2</v>
       </c>
       <c r="C277" t="n">
         <v>48.86</v>
@@ -6819,7 +6819,7 @@
         <v>0.64</v>
       </c>
       <c r="B278" t="n">
-        <v>6.1541111</v>
+        <v>76.42</v>
       </c>
       <c r="C278" t="n">
         <v>123.47</v>
@@ -6842,7 +6842,7 @@
         <v>1.18</v>
       </c>
       <c r="B279" t="n">
-        <v>6.1541111</v>
+        <v>72.22</v>
       </c>
       <c r="C279" t="n">
         <v>60.29</v>
@@ -6865,7 +6865,7 @@
         <v>2.2</v>
       </c>
       <c r="B280" t="n">
-        <v>6.1541111</v>
+        <v>99.87</v>
       </c>
       <c r="C280" t="n">
         <v>213.47</v>
@@ -6888,7 +6888,7 @@
         <v>2.36</v>
       </c>
       <c r="B281" t="n">
-        <v>6.1541111</v>
+        <v>88.72</v>
       </c>
       <c r="C281" t="n">
         <v>192</v>
@@ -6911,7 +6911,7 @@
         <v>1.6</v>
       </c>
       <c r="B282" t="n">
-        <v>6.1541111</v>
+        <v>91.33</v>
       </c>
       <c r="C282" t="n">
         <v>151.52</v>
@@ -6934,7 +6934,7 @@
         <v>4.36</v>
       </c>
       <c r="B283" t="n">
-        <v>6.1541111</v>
+        <v>64.64</v>
       </c>
       <c r="C283" t="n">
         <v>159.47</v>
@@ -6957,7 +6957,7 @@
         <v>0.5</v>
       </c>
       <c r="B284" t="n">
-        <v>6.1541111</v>
+        <v>96.7</v>
       </c>
       <c r="C284" t="n">
         <v>174.23</v>
@@ -6980,7 +6980,7 @@
         <v>1.35</v>
       </c>
       <c r="B285" t="n">
-        <v>6.1541111</v>
+        <v>91.02</v>
       </c>
       <c r="C285" t="n">
         <v>165.44</v>
@@ -7003,7 +7003,7 @@
         <v>1.06</v>
       </c>
       <c r="B286" t="n">
-        <v>6.1541111</v>
+        <v>72.25</v>
       </c>
       <c r="C286" t="n">
         <v>105.17</v>
@@ -7026,7 +7026,7 @@
         <v>2.93</v>
       </c>
       <c r="B287" t="n">
-        <v>6.1541111</v>
+        <v>79.91</v>
       </c>
       <c r="C287" t="n">
         <v>115.39</v>
@@ -7049,7 +7049,7 @@
         <v>1.58</v>
       </c>
       <c r="B288" t="n">
-        <v>6.1541111</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="C288" t="n">
         <v>134.57</v>
@@ -7072,7 +7072,7 @@
         <v>2.43</v>
       </c>
       <c r="B289" t="n">
-        <v>6.1541111</v>
+        <v>86.2</v>
       </c>
       <c r="C289" t="n">
         <v>98.54000000000001</v>
@@ -7095,7 +7095,7 @@
         <v>4.36</v>
       </c>
       <c r="B290" t="n">
-        <v>6.1541111</v>
+        <v>82.06999999999999</v>
       </c>
       <c r="C290" t="n">
         <v>228.85</v>
@@ -7118,7 +7118,7 @@
         <v>2.88</v>
       </c>
       <c r="B291" t="n">
-        <v>6.1541111</v>
+        <v>84.33</v>
       </c>
       <c r="C291" t="n">
         <v>111.89</v>
@@ -7141,7 +7141,7 @@
         <v>2.21</v>
       </c>
       <c r="B292" t="n">
-        <v>6.1541111</v>
+        <v>82.55</v>
       </c>
       <c r="C292" t="n">
         <v>255.72</v>
@@ -7164,7 +7164,7 @@
         <v>3.01</v>
       </c>
       <c r="B293" t="n">
-        <v>6.1541111</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="C293" t="n">
         <v>120.63</v>
@@ -7187,7 +7187,7 @@
         <v>4.04</v>
       </c>
       <c r="B294" t="n">
-        <v>6.1541111</v>
+        <v>103.23</v>
       </c>
       <c r="C294" t="n">
         <v>112.04</v>
@@ -7210,7 +7210,7 @@
         <v>2.28</v>
       </c>
       <c r="B295" t="n">
-        <v>6.1541111</v>
+        <v>60.37</v>
       </c>
       <c r="C295" t="n">
         <v>211.26</v>
@@ -7233,7 +7233,7 @@
         <v>2.34</v>
       </c>
       <c r="B296" t="n">
-        <v>6.1541111</v>
+        <v>82.73</v>
       </c>
       <c r="C296" t="n">
         <v>168.11</v>
@@ -7256,7 +7256,7 @@
         <v>2.74</v>
       </c>
       <c r="B297" t="n">
-        <v>6.1541111</v>
+        <v>87.69</v>
       </c>
       <c r="C297" t="n">
         <v>100.24</v>
@@ -7279,7 +7279,7 @@
         <v>5</v>
       </c>
       <c r="B298" t="n">
-        <v>6.1541111</v>
+        <v>89.12</v>
       </c>
       <c r="C298" t="n">
         <v>94.65000000000001</v>
@@ -7302,7 +7302,7 @@
         <v>3.31</v>
       </c>
       <c r="B299" t="n">
-        <v>6.1541111</v>
+        <v>81.11</v>
       </c>
       <c r="C299" t="n">
         <v>118.55</v>
@@ -7325,7 +7325,7 @@
         <v>3.01</v>
       </c>
       <c r="B300" t="n">
-        <v>6.1541111</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="C300" t="n">
         <v>154.85</v>
@@ -7348,7 +7348,7 @@
         <v>4.13</v>
       </c>
       <c r="B301" t="n">
-        <v>6.1541111</v>
+        <v>89.51000000000001</v>
       </c>
       <c r="C301" t="n">
         <v>135.83</v>
@@ -7371,7 +7371,7 @@
         <v>1.17</v>
       </c>
       <c r="B302" t="n">
-        <v>6.1541111</v>
+        <v>106.3</v>
       </c>
       <c r="C302" t="n">
         <v>151.24</v>
@@ -7394,7 +7394,7 @@
         <v>1.51</v>
       </c>
       <c r="B303" t="n">
-        <v>6.1541111</v>
+        <v>67.17</v>
       </c>
       <c r="C303" t="n">
         <v>241.41</v>
@@ -7417,7 +7417,7 @@
         <v>2.45</v>
       </c>
       <c r="B304" t="n">
-        <v>6.1541111</v>
+        <v>95.94</v>
       </c>
       <c r="C304" t="n">
         <v>159.99</v>
@@ -7440,7 +7440,7 @@
         <v>2.04</v>
       </c>
       <c r="B305" t="n">
-        <v>6.1541111</v>
+        <v>81.63</v>
       </c>
       <c r="C305" t="n">
         <v>49.99</v>
@@ -7463,7 +7463,7 @@
         <v>2.45</v>
       </c>
       <c r="B306" t="n">
-        <v>6.1541111</v>
+        <v>84.84</v>
       </c>
       <c r="C306" t="n">
         <v>95.31999999999999</v>
@@ -7486,7 +7486,7 @@
         <v>1.99</v>
       </c>
       <c r="B307" t="n">
-        <v>6.1541111</v>
+        <v>72.94</v>
       </c>
       <c r="C307" t="n">
         <v>136.51</v>
@@ -7509,7 +7509,7 @@
         <v>0.72</v>
       </c>
       <c r="B308" t="n">
-        <v>6.1541111</v>
+        <v>81.56</v>
       </c>
       <c r="C308" t="n">
         <v>253.4</v>
@@ -7532,7 +7532,7 @@
         <v>1.72</v>
       </c>
       <c r="B309" t="n">
-        <v>6.1541111</v>
+        <v>101.17</v>
       </c>
       <c r="C309" t="n">
         <v>218.02</v>
@@ -7555,7 +7555,7 @@
         <v>1.91</v>
       </c>
       <c r="B310" t="n">
-        <v>6.1541111</v>
+        <v>92.56</v>
       </c>
       <c r="C310" t="n">
         <v>238.79</v>
@@ -7578,7 +7578,7 @@
         <v>2.96</v>
       </c>
       <c r="B311" t="n">
-        <v>6.1541111</v>
+        <v>106.36</v>
       </c>
       <c r="C311" t="n">
         <v>134.59</v>
@@ -7601,7 +7601,7 @@
         <v>3.02</v>
       </c>
       <c r="B312" t="n">
-        <v>6.1541111</v>
+        <v>99.7</v>
       </c>
       <c r="C312" t="n">
         <v>150.94</v>
@@ -7624,7 +7624,7 @@
         <v>1.41</v>
       </c>
       <c r="B313" t="n">
-        <v>6.1541111</v>
+        <v>90.84</v>
       </c>
       <c r="C313" t="n">
         <v>40</v>
@@ -7647,7 +7647,7 @@
         <v>1.27</v>
       </c>
       <c r="B314" t="n">
-        <v>6.1541111</v>
+        <v>106.5</v>
       </c>
       <c r="C314" t="n">
         <v>123.66</v>
@@ -7670,7 +7670,7 @@
         <v>1.34</v>
       </c>
       <c r="B315" t="n">
-        <v>6.1541111</v>
+        <v>90.84</v>
       </c>
       <c r="C315" t="n">
         <v>154.91</v>
@@ -7693,7 +7693,7 @@
         <v>1.39</v>
       </c>
       <c r="B316" t="n">
-        <v>6.1541111</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="C316" t="n">
         <v>114.69</v>
@@ -7716,7 +7716,7 @@
         <v>1.78</v>
       </c>
       <c r="B317" t="n">
-        <v>6.1541111</v>
+        <v>82.01000000000001</v>
       </c>
       <c r="C317" t="n">
         <v>170.61</v>
@@ -7739,7 +7739,7 @@
         <v>1.65</v>
       </c>
       <c r="B318" t="n">
-        <v>6.1541111</v>
+        <v>86.37</v>
       </c>
       <c r="C318" t="n">
         <v>118.39</v>
@@ -7762,7 +7762,7 @@
         <v>1.33</v>
       </c>
       <c r="B319" t="n">
-        <v>6.1541111</v>
+        <v>77.2</v>
       </c>
       <c r="C319" t="n">
         <v>153.34</v>
@@ -7785,7 +7785,7 @@
         <v>2.41</v>
       </c>
       <c r="B320" t="n">
-        <v>6.1541111</v>
+        <v>97.45</v>
       </c>
       <c r="C320" t="n">
         <v>210.38</v>
@@ -7808,7 +7808,7 @@
         <v>2.64</v>
       </c>
       <c r="B321" t="n">
-        <v>6.1541111</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="C321" t="n">
         <v>124.57</v>
@@ -7831,7 +7831,7 @@
         <v>1.67</v>
       </c>
       <c r="B322" t="n">
-        <v>6.1541111</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="C322" t="n">
         <v>146.64</v>
@@ -7854,7 +7854,7 @@
         <v>1.1</v>
       </c>
       <c r="B323" t="n">
-        <v>6.1541111</v>
+        <v>83.28</v>
       </c>
       <c r="C323" t="n">
         <v>150.41</v>
@@ -7877,7 +7877,7 @@
         <v>1.47</v>
       </c>
       <c r="B324" t="n">
-        <v>6.1541111</v>
+        <v>99.63</v>
       </c>
       <c r="C324" t="n">
         <v>148.99</v>
@@ -7900,7 +7900,7 @@
         <v>2.15</v>
       </c>
       <c r="B325" t="n">
-        <v>6.1541111</v>
+        <v>94.58</v>
       </c>
       <c r="C325" t="n">
         <v>299.54</v>
@@ -7923,7 +7923,7 @@
         <v>2.86</v>
       </c>
       <c r="B326" t="n">
-        <v>6.1541111</v>
+        <v>107.42</v>
       </c>
       <c r="C326" t="n">
         <v>128.49</v>
@@ -7946,7 +7946,7 @@
         <v>1.59</v>
       </c>
       <c r="B327" t="n">
-        <v>6.1541111</v>
+        <v>94.34</v>
       </c>
       <c r="C327" t="n">
         <v>178.88</v>
@@ -7969,7 +7969,7 @@
         <v>3.13</v>
       </c>
       <c r="B328" t="n">
-        <v>6.1541111</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="C328" t="n">
         <v>261.4</v>
@@ -7992,7 +7992,7 @@
         <v>0.5</v>
       </c>
       <c r="B329" t="n">
-        <v>6.1541111</v>
+        <v>84.77</v>
       </c>
       <c r="C329" t="n">
         <v>199.93</v>
@@ -8015,7 +8015,7 @@
         <v>2.46</v>
       </c>
       <c r="B330" t="n">
-        <v>6.1541111</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="C330" t="n">
         <v>113.8</v>
@@ -8038,7 +8038,7 @@
         <v>1.28</v>
       </c>
       <c r="B331" t="n">
-        <v>6.1541111</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="C331" t="n">
         <v>143.48</v>
@@ -8061,7 +8061,7 @@
         <v>2.75</v>
       </c>
       <c r="B332" t="n">
-        <v>6.1541111</v>
+        <v>103.71</v>
       </c>
       <c r="C332" t="n">
         <v>149.24</v>
@@ -8084,7 +8084,7 @@
         <v>2.64</v>
       </c>
       <c r="B333" t="n">
-        <v>6.1541111</v>
+        <v>93.22</v>
       </c>
       <c r="C333" t="n">
         <v>447.28</v>
@@ -8107,7 +8107,7 @@
         <v>2.29</v>
       </c>
       <c r="B334" t="n">
-        <v>6.1541111</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="C334" t="n">
         <v>70.51000000000001</v>
@@ -8130,7 +8130,7 @@
         <v>3.66</v>
       </c>
       <c r="B335" t="n">
-        <v>6.1541111</v>
+        <v>73.41</v>
       </c>
       <c r="C335" t="n">
         <v>130.19</v>
@@ -8153,7 +8153,7 @@
         <v>1.44</v>
       </c>
       <c r="B336" t="n">
-        <v>6.1541111</v>
+        <v>85.97</v>
       </c>
       <c r="C336" t="n">
         <v>175.34</v>
@@ -8176,7 +8176,7 @@
         <v>2.93</v>
       </c>
       <c r="B337" t="n">
-        <v>6.1541111</v>
+        <v>70.97</v>
       </c>
       <c r="C337" t="n">
         <v>246.27</v>
@@ -8199,7 +8199,7 @@
         <v>1.95</v>
       </c>
       <c r="B338" t="n">
-        <v>6.1541111</v>
+        <v>77.52</v>
       </c>
       <c r="C338" t="n">
         <v>49.13</v>
@@ -8222,7 +8222,7 @@
         <v>1.47</v>
       </c>
       <c r="B339" t="n">
-        <v>6.1541111</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="C339" t="n">
         <v>259.25</v>
@@ -8245,7 +8245,7 @@
         <v>4.3</v>
       </c>
       <c r="B340" t="n">
-        <v>6.1541111</v>
+        <v>99.44</v>
       </c>
       <c r="C340" t="n">
         <v>129.7</v>
@@ -8268,7 +8268,7 @@
         <v>2.8</v>
       </c>
       <c r="B341" t="n">
-        <v>6.1541111</v>
+        <v>92.88</v>
       </c>
       <c r="C341" t="n">
         <v>144.25</v>
@@ -8291,7 +8291,7 @@
         <v>2.13</v>
       </c>
       <c r="B342" t="n">
-        <v>6.1541111</v>
+        <v>60.37</v>
       </c>
       <c r="C342" t="n">
         <v>216.4</v>
@@ -8314,7 +8314,7 @@
         <v>1.89</v>
       </c>
       <c r="B343" t="n">
-        <v>6.1541111</v>
+        <v>89.22</v>
       </c>
       <c r="C343" t="n">
         <v>134.16</v>
@@ -8337,7 +8337,7 @@
         <v>3.01</v>
       </c>
       <c r="B344" t="n">
-        <v>6.1541111</v>
+        <v>86.44</v>
       </c>
       <c r="C344" t="n">
         <v>167.34</v>
@@ -8360,7 +8360,7 @@
         <v>1.5</v>
       </c>
       <c r="B345" t="n">
-        <v>6.1541111</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="C345" t="n">
         <v>220.35</v>
@@ -8383,7 +8383,7 @@
         <v>1.55</v>
       </c>
       <c r="B346" t="n">
-        <v>6.1541111</v>
+        <v>104.97</v>
       </c>
       <c r="C346" t="n">
         <v>113.23</v>
@@ -8406,7 +8406,7 @@
         <v>1.95</v>
       </c>
       <c r="B347" t="n">
-        <v>6.1541111</v>
+        <v>60.81</v>
       </c>
       <c r="C347" t="n">
         <v>242.22</v>
@@ -8429,7 +8429,7 @@
         <v>2.69</v>
       </c>
       <c r="B348" t="n">
-        <v>6.1541111</v>
+        <v>78.48</v>
       </c>
       <c r="C348" t="n">
         <v>222.95</v>
@@ -8452,7 +8452,7 @@
         <v>2.83</v>
       </c>
       <c r="B349" t="n">
-        <v>6.1541111</v>
+        <v>92.66</v>
       </c>
       <c r="C349" t="n">
         <v>121.15</v>
@@ -8475,7 +8475,7 @@
         <v>3.53</v>
       </c>
       <c r="B350" t="n">
-        <v>6.1541111</v>
+        <v>66.59</v>
       </c>
       <c r="C350" t="n">
         <v>220.49</v>
@@ -8498,7 +8498,7 @@
         <v>3.69</v>
       </c>
       <c r="B351" t="n">
-        <v>6.1541111</v>
+        <v>103.28</v>
       </c>
       <c r="C351" t="n">
         <v>144.82</v>
@@ -8521,7 +8521,7 @@
         <v>2.11</v>
       </c>
       <c r="B352" t="n">
-        <v>6.1541111</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="C352" t="n">
         <v>161.58</v>
@@ -8544,7 +8544,7 @@
         <v>0.5</v>
       </c>
       <c r="B353" t="n">
-        <v>6.1541111</v>
+        <v>95.73</v>
       </c>
       <c r="C353" t="n">
         <v>402.48</v>
@@ -8567,7 +8567,7 @@
         <v>3.46</v>
       </c>
       <c r="B354" t="n">
-        <v>6.1541111</v>
+        <v>78.72</v>
       </c>
       <c r="C354" t="n">
         <v>203.96</v>
@@ -8590,7 +8590,7 @@
         <v>1.63</v>
       </c>
       <c r="B355" t="n">
-        <v>6.1541111</v>
+        <v>95.34</v>
       </c>
       <c r="C355" t="n">
         <v>122.94</v>
@@ -8613,7 +8613,7 @@
         <v>1.63</v>
       </c>
       <c r="B356" t="n">
-        <v>6.1541111</v>
+        <v>98.39</v>
       </c>
       <c r="C356" t="n">
         <v>225.07</v>
@@ -8636,7 +8636,7 @@
         <v>1.31</v>
       </c>
       <c r="B357" t="n">
-        <v>6.1541111</v>
+        <v>88.37</v>
       </c>
       <c r="C357" t="n">
         <v>161.95</v>
@@ -8659,7 +8659,7 @@
         <v>3.6</v>
       </c>
       <c r="B358" t="n">
-        <v>6.1541111</v>
+        <v>88.38</v>
       </c>
       <c r="C358" t="n">
         <v>55.32</v>
@@ -8682,7 +8682,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="B359" t="n">
-        <v>6.1541111</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="C359" t="n">
         <v>204.41</v>
@@ -8705,7 +8705,7 @@
         <v>0.66</v>
       </c>
       <c r="B360" t="n">
-        <v>6.1541111</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="C360" t="n">
         <v>82.75</v>
@@ -8728,7 +8728,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="B361" t="n">
-        <v>6.1541111</v>
+        <v>83.8</v>
       </c>
       <c r="C361" t="n">
         <v>133.18</v>
@@ -8751,7 +8751,7 @@
         <v>1.26</v>
       </c>
       <c r="B362" t="n">
-        <v>6.1541111</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="C362" t="n">
         <v>110.14</v>
@@ -8774,7 +8774,7 @@
         <v>3.36</v>
       </c>
       <c r="B363" t="n">
-        <v>6.1541111</v>
+        <v>90.17</v>
       </c>
       <c r="C363" t="n">
         <v>89.94</v>
@@ -8797,7 +8797,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B364" t="n">
-        <v>6.1541111</v>
+        <v>97.56999999999999</v>
       </c>
       <c r="C364" t="n">
         <v>110.44</v>
@@ -8820,7 +8820,7 @@
         <v>1.95</v>
       </c>
       <c r="B365" t="n">
-        <v>6.1541111</v>
+        <v>72.87</v>
       </c>
       <c r="C365" t="n">
         <v>166.63</v>
@@ -8843,7 +8843,7 @@
         <v>3.12</v>
       </c>
       <c r="B366" t="n">
-        <v>6.1541111</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="C366" t="n">
         <v>184.59</v>
@@ -8866,7 +8866,7 @@
         <v>2.45</v>
       </c>
       <c r="B367" t="n">
-        <v>6.1541111</v>
+        <v>103.35</v>
       </c>
       <c r="C367" t="n">
         <v>52.18</v>
@@ -8889,7 +8889,7 @@
         <v>2.72</v>
       </c>
       <c r="B368" t="n">
-        <v>6.1541111</v>
+        <v>76.65000000000001</v>
       </c>
       <c r="C368" t="n">
         <v>450.23</v>
@@ -8912,7 +8912,7 @@
         <v>2.46</v>
       </c>
       <c r="B369" t="n">
-        <v>6.1541111</v>
+        <v>75.7</v>
       </c>
       <c r="C369" t="n">
         <v>163.39</v>
@@ -8935,7 +8935,7 @@
         <v>1.95</v>
       </c>
       <c r="B370" t="n">
-        <v>6.1541111</v>
+        <v>88</v>
       </c>
       <c r="C370" t="n">
         <v>149.85</v>
@@ -8958,7 +8958,7 @@
         <v>5</v>
       </c>
       <c r="B371" t="n">
-        <v>6.1541111</v>
+        <v>95.7</v>
       </c>
       <c r="C371" t="n">
         <v>58.98</v>
@@ -8981,7 +8981,7 @@
         <v>2.46</v>
       </c>
       <c r="B372" t="n">
-        <v>6.1541111</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="C372" t="n">
         <v>185.32</v>
@@ -9004,7 +9004,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="B373" t="n">
-        <v>6.1541111</v>
+        <v>101.52</v>
       </c>
       <c r="C373" t="n">
         <v>249.15</v>
@@ -9027,7 +9027,7 @@
         <v>2.42</v>
       </c>
       <c r="B374" t="n">
-        <v>6.1541111</v>
+        <v>95.84999999999999</v>
       </c>
       <c r="C374" t="n">
         <v>140.15</v>
@@ -9050,7 +9050,7 @@
         <v>2.42</v>
       </c>
       <c r="B375" t="n">
-        <v>6.1541111</v>
+        <v>95.67</v>
       </c>
       <c r="C375" t="n">
         <v>170.96</v>
@@ -9073,7 +9073,7 @@
         <v>2.29</v>
       </c>
       <c r="B376" t="n">
-        <v>6.1541111</v>
+        <v>92.22</v>
       </c>
       <c r="C376" t="n">
         <v>106.64</v>
@@ -9096,7 +9096,7 @@
         <v>3.42</v>
       </c>
       <c r="B377" t="n">
-        <v>6.1541111</v>
+        <v>110.01</v>
       </c>
       <c r="C377" t="n">
         <v>174.17</v>
@@ -9119,7 +9119,7 @@
         <v>2.48</v>
       </c>
       <c r="B378" t="n">
-        <v>6.1541111</v>
+        <v>83.11</v>
       </c>
       <c r="C378" t="n">
         <v>88.58</v>
@@ -9142,7 +9142,7 @@
         <v>2.94</v>
       </c>
       <c r="B379" t="n">
-        <v>6.1541111</v>
+        <v>61.53</v>
       </c>
       <c r="C379" t="n">
         <v>185.43</v>
@@ -9165,7 +9165,7 @@
         <v>0.57</v>
       </c>
       <c r="B380" t="n">
-        <v>6.1541111</v>
+        <v>104.82</v>
       </c>
       <c r="C380" t="n">
         <v>96.72</v>
@@ -9188,7 +9188,7 @@
         <v>1.43</v>
       </c>
       <c r="B381" t="n">
-        <v>6.1541111</v>
+        <v>80.08</v>
       </c>
       <c r="C381" t="n">
         <v>229.41</v>
@@ -9211,7 +9211,7 @@
         <v>2.63</v>
       </c>
       <c r="B382" t="n">
-        <v>6.1541111</v>
+        <v>86.87</v>
       </c>
       <c r="C382" t="n">
         <v>178.55</v>
@@ -9234,7 +9234,7 @@
         <v>4.79</v>
       </c>
       <c r="B383" t="n">
-        <v>6.1541111</v>
+        <v>101.29</v>
       </c>
       <c r="C383" t="n">
         <v>50.76</v>
@@ -9257,7 +9257,7 @@
         <v>1.89</v>
       </c>
       <c r="B384" t="n">
-        <v>6.1541111</v>
+        <v>66.34</v>
       </c>
       <c r="C384" t="n">
         <v>138.56</v>
@@ -9280,7 +9280,7 @@
         <v>0.73</v>
       </c>
       <c r="B385" t="n">
-        <v>6.1541111</v>
+        <v>70.55</v>
       </c>
       <c r="C385" t="n">
         <v>199.77</v>
@@ -9303,7 +9303,7 @@
         <v>2.07</v>
       </c>
       <c r="B386" t="n">
-        <v>6.1541111</v>
+        <v>66.36</v>
       </c>
       <c r="C386" t="n">
         <v>51.63</v>
@@ -9326,7 +9326,7 @@
         <v>1.87</v>
       </c>
       <c r="B387" t="n">
-        <v>6.1541111</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="C387" t="n">
         <v>277.19</v>
@@ -9349,7 +9349,7 @@
         <v>2.87</v>
       </c>
       <c r="B388" t="n">
-        <v>6.1541111</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="C388" t="n">
         <v>129.78</v>
@@ -9372,7 +9372,7 @@
         <v>2.44</v>
       </c>
       <c r="B389" t="n">
-        <v>6.1541111</v>
+        <v>91.86</v>
       </c>
       <c r="C389" t="n">
         <v>213.01</v>
@@ -9395,7 +9395,7 @@
         <v>2.83</v>
       </c>
       <c r="B390" t="n">
-        <v>6.1541111</v>
+        <v>88.89</v>
       </c>
       <c r="C390" t="n">
         <v>190.57</v>
@@ -9418,7 +9418,7 @@
         <v>2.81</v>
       </c>
       <c r="B391" t="n">
-        <v>6.1541111</v>
+        <v>68.62</v>
       </c>
       <c r="C391" t="n">
         <v>142.34</v>
@@ -9441,7 +9441,7 @@
         <v>0.88</v>
       </c>
       <c r="B392" t="n">
-        <v>6.1541111</v>
+        <v>60.37</v>
       </c>
       <c r="C392" t="n">
         <v>259.48</v>
@@ -9464,7 +9464,7 @@
         <v>3.24</v>
       </c>
       <c r="B393" t="n">
-        <v>6.1541111</v>
+        <v>86.22</v>
       </c>
       <c r="C393" t="n">
         <v>44.57</v>
@@ -9487,7 +9487,7 @@
         <v>3.43</v>
       </c>
       <c r="B394" t="n">
-        <v>6.1541111</v>
+        <v>79.91</v>
       </c>
       <c r="C394" t="n">
         <v>41.57</v>
@@ -9510,7 +9510,7 @@
         <v>4.59</v>
       </c>
       <c r="B395" t="n">
-        <v>6.1541111</v>
+        <v>91.08</v>
       </c>
       <c r="C395" t="n">
         <v>134.3</v>
@@ -9533,7 +9533,7 @@
         <v>4.41</v>
       </c>
       <c r="B396" t="n">
-        <v>6.1541111</v>
+        <v>94</v>
       </c>
       <c r="C396" t="n">
         <v>188.37</v>
@@ -9556,7 +9556,7 @@
         <v>2.38</v>
       </c>
       <c r="B397" t="n">
-        <v>6.1541111</v>
+        <v>87.23</v>
       </c>
       <c r="C397" t="n">
         <v>106.37</v>
@@ -9579,7 +9579,7 @@
         <v>0.5</v>
       </c>
       <c r="B398" t="n">
-        <v>6.1541111</v>
+        <v>94.69</v>
       </c>
       <c r="C398" t="n">
         <v>147.05</v>
@@ -9602,7 +9602,7 @@
         <v>0.5</v>
       </c>
       <c r="B399" t="n">
-        <v>6.1541111</v>
+        <v>88.31999999999999</v>
       </c>
       <c r="C399" t="n">
         <v>127.81</v>
@@ -9625,7 +9625,7 @@
         <v>2.67</v>
       </c>
       <c r="B400" t="n">
-        <v>6.1541111</v>
+        <v>91.93000000000001</v>
       </c>
       <c r="C400" t="n">
         <v>120.23</v>
@@ -9648,7 +9648,7 @@
         <v>3.53</v>
       </c>
       <c r="B401" t="n">
-        <v>6.1541111</v>
+        <v>77.12</v>
       </c>
       <c r="C401" t="n">
         <v>88.73</v>
@@ -9671,7 +9671,7 @@
         <v>2.71</v>
       </c>
       <c r="B402" t="n">
-        <v>6.1541111</v>
+        <v>83.42</v>
       </c>
       <c r="C402" t="n">
         <v>98.79000000000001</v>
@@ -9694,7 +9694,7 @@
         <v>2.82</v>
       </c>
       <c r="B403" t="n">
-        <v>6.1541111</v>
+        <v>87.93000000000001</v>
       </c>
       <c r="C403" t="n">
         <v>456.28</v>
@@ -9717,7 +9717,7 @@
         <v>1.29</v>
       </c>
       <c r="B404" t="n">
-        <v>6.1541111</v>
+        <v>95.42</v>
       </c>
       <c r="C404" t="n">
         <v>152.57</v>
@@ -9740,7 +9740,7 @@
         <v>3.59</v>
       </c>
       <c r="B405" t="n">
-        <v>6.1541111</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="C405" t="n">
         <v>50.75</v>
@@ -9763,7 +9763,7 @@
         <v>2.01</v>
       </c>
       <c r="B406" t="n">
-        <v>6.1541111</v>
+        <v>91.83</v>
       </c>
       <c r="C406" t="n">
         <v>61.47</v>
@@ -9786,7 +9786,7 @@
         <v>2.28</v>
       </c>
       <c r="B407" t="n">
-        <v>6.1541111</v>
+        <v>82.38</v>
       </c>
       <c r="C407" t="n">
         <v>123.53</v>
@@ -9809,7 +9809,7 @@
         <v>3.34</v>
       </c>
       <c r="B408" t="n">
-        <v>6.1541111</v>
+        <v>84.16</v>
       </c>
       <c r="C408" t="n">
         <v>267.46</v>
@@ -9832,7 +9832,7 @@
         <v>2.98</v>
       </c>
       <c r="B409" t="n">
-        <v>6.1541111</v>
+        <v>95.53</v>
       </c>
       <c r="C409" t="n">
         <v>227.54</v>
@@ -9855,7 +9855,7 @@
         <v>3.41</v>
       </c>
       <c r="B410" t="n">
-        <v>6.1541111</v>
+        <v>61.66</v>
       </c>
       <c r="C410" t="n">
         <v>106.78</v>
@@ -9878,7 +9878,7 @@
         <v>2.29</v>
       </c>
       <c r="B411" t="n">
-        <v>6.1541111</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="C411" t="n">
         <v>336.74</v>
@@ -9901,7 +9901,7 @@
         <v>2.56</v>
       </c>
       <c r="B412" t="n">
-        <v>6.1541111</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="C412" t="n">
         <v>74.11</v>
@@ -9924,7 +9924,7 @@
         <v>0.55</v>
       </c>
       <c r="B413" t="n">
-        <v>6.1541111</v>
+        <v>60.37</v>
       </c>
       <c r="C413" t="n">
         <v>56.08</v>
@@ -9947,7 +9947,7 @@
         <v>4.11</v>
       </c>
       <c r="B414" t="n">
-        <v>6.1541111</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="C414" t="n">
         <v>147.63</v>
@@ -9970,7 +9970,7 @@
         <v>0.82</v>
       </c>
       <c r="B415" t="n">
-        <v>6.1541111</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="C415" t="n">
         <v>108.76</v>
@@ -9993,7 +9993,7 @@
         <v>2.64</v>
       </c>
       <c r="B416" t="n">
-        <v>6.1541111</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="C416" t="n">
         <v>123.24</v>
@@ -10016,7 +10016,7 @@
         <v>2.76</v>
       </c>
       <c r="B417" t="n">
-        <v>6.1541111</v>
+        <v>87.95</v>
       </c>
       <c r="C417" t="n">
         <v>192.18</v>
@@ -10039,7 +10039,7 @@
         <v>3.7</v>
       </c>
       <c r="B418" t="n">
-        <v>6.1541111</v>
+        <v>98.64</v>
       </c>
       <c r="C418" t="n">
         <v>147.07</v>
@@ -10062,7 +10062,7 @@
         <v>2.55</v>
       </c>
       <c r="B419" t="n">
-        <v>6.1541111</v>
+        <v>101.5</v>
       </c>
       <c r="C419" t="n">
         <v>164.8</v>
@@ -10085,7 +10085,7 @@
         <v>1.91</v>
       </c>
       <c r="B420" t="n">
-        <v>6.1541111</v>
+        <v>84.73999999999999</v>
       </c>
       <c r="C420" t="n">
         <v>257.26</v>
@@ -10108,7 +10108,7 @@
         <v>1.43</v>
       </c>
       <c r="B421" t="n">
-        <v>6.1541111</v>
+        <v>101.81</v>
       </c>
       <c r="C421" t="n">
         <v>230.52</v>
@@ -10131,7 +10131,7 @@
         <v>1.71</v>
       </c>
       <c r="B422" t="n">
-        <v>6.1541111</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="C422" t="n">
         <v>206.73</v>
@@ -10154,7 +10154,7 @@
         <v>2.48</v>
       </c>
       <c r="B423" t="n">
-        <v>6.1541111</v>
+        <v>75.52</v>
       </c>
       <c r="C423" t="n">
         <v>161.74</v>
@@ -10177,7 +10177,7 @@
         <v>1.22</v>
       </c>
       <c r="B424" t="n">
-        <v>6.1541111</v>
+        <v>78.44</v>
       </c>
       <c r="C424" t="n">
         <v>54.32</v>
@@ -10200,7 +10200,7 @@
         <v>3.11</v>
       </c>
       <c r="B425" t="n">
-        <v>6.1541111</v>
+        <v>67.81</v>
       </c>
       <c r="C425" t="n">
         <v>166.18</v>
@@ -10223,7 +10223,7 @@
         <v>2.19</v>
       </c>
       <c r="B426" t="n">
-        <v>6.1541111</v>
+        <v>74.91</v>
       </c>
       <c r="C426" t="n">
         <v>136.34</v>
@@ -10246,7 +10246,7 @@
         <v>0.84</v>
       </c>
       <c r="B427" t="n">
-        <v>6.1541111</v>
+        <v>81.28</v>
       </c>
       <c r="C427" t="n">
         <v>244.11</v>
@@ -10269,7 +10269,7 @@
         <v>0.99</v>
       </c>
       <c r="B428" t="n">
-        <v>6.1541111</v>
+        <v>95.20999999999999</v>
       </c>
       <c r="C428" t="n">
         <v>197.82</v>
@@ -10292,7 +10292,7 @@
         <v>4.83</v>
       </c>
       <c r="B429" t="n">
-        <v>6.1541111</v>
+        <v>106.22</v>
       </c>
       <c r="C429" t="n">
         <v>123.41</v>
@@ -10315,7 +10315,7 @@
         <v>1.52</v>
       </c>
       <c r="B430" t="n">
-        <v>6.1541111</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="C430" t="n">
         <v>269.52</v>
@@ -10338,7 +10338,7 @@
         <v>2.5</v>
       </c>
       <c r="B431" t="n">
-        <v>6.1541111</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="C431" t="n">
         <v>133.33</v>
@@ -10361,7 +10361,7 @@
         <v>1.97</v>
       </c>
       <c r="B432" t="n">
-        <v>6.1541111</v>
+        <v>73.09</v>
       </c>
       <c r="C432" t="n">
         <v>129.48</v>
@@ -10384,7 +10384,7 @@
         <v>1.18</v>
       </c>
       <c r="B433" t="n">
-        <v>6.1541111</v>
+        <v>91.27</v>
       </c>
       <c r="C433" t="n">
         <v>189.76</v>
@@ -10407,7 +10407,7 @@
         <v>1.1</v>
       </c>
       <c r="B434" t="n">
-        <v>6.1541111</v>
+        <v>84</v>
       </c>
       <c r="C434" t="n">
         <v>123.91</v>
@@ -10430,7 +10430,7 @@
         <v>3.14</v>
       </c>
       <c r="B435" t="n">
-        <v>6.1541111</v>
+        <v>63.6</v>
       </c>
       <c r="C435" t="n">
         <v>106.05</v>
@@ -10453,7 +10453,7 @@
         <v>2.43</v>
       </c>
       <c r="B436" t="n">
-        <v>6.1541111</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="C436" t="n">
         <v>80.87</v>
@@ -10476,7 +10476,7 @@
         <v>1.6</v>
       </c>
       <c r="B437" t="n">
-        <v>6.1541111</v>
+        <v>78.31</v>
       </c>
       <c r="C437" t="n">
         <v>111.29</v>
@@ -10499,7 +10499,7 @@
         <v>1.74</v>
       </c>
       <c r="B438" t="n">
-        <v>6.1541111</v>
+        <v>79.17</v>
       </c>
       <c r="C438" t="n">
         <v>171.43</v>
@@ -10522,7 +10522,7 @@
         <v>2.08</v>
       </c>
       <c r="B439" t="n">
-        <v>6.1541111</v>
+        <v>72.73</v>
       </c>
       <c r="C439" t="n">
         <v>139.53</v>
@@ -10545,7 +10545,7 @@
         <v>2.55</v>
       </c>
       <c r="B440" t="n">
-        <v>6.1541111</v>
+        <v>77.72</v>
       </c>
       <c r="C440" t="n">
         <v>119.89</v>
@@ -10568,7 +10568,7 @@
         <v>2.45</v>
       </c>
       <c r="B441" t="n">
-        <v>6.1541111</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="C441" t="n">
         <v>147.98</v>
@@ -10591,7 +10591,7 @@
         <v>2.44</v>
       </c>
       <c r="B442" t="n">
-        <v>6.1541111</v>
+        <v>83.3</v>
       </c>
       <c r="C442" t="n">
         <v>118.71</v>
@@ -10614,7 +10614,7 @@
         <v>1.09</v>
       </c>
       <c r="B443" t="n">
-        <v>6.1541111</v>
+        <v>89.52</v>
       </c>
       <c r="C443" t="n">
         <v>128.81</v>
@@ -10637,7 +10637,7 @@
         <v>4.35</v>
       </c>
       <c r="B444" t="n">
-        <v>6.1541111</v>
+        <v>89.91</v>
       </c>
       <c r="C444" t="n">
         <v>69.63</v>
@@ -10660,7 +10660,7 @@
         <v>1.07</v>
       </c>
       <c r="B445" t="n">
-        <v>6.1541111</v>
+        <v>101.42</v>
       </c>
       <c r="C445" t="n">
         <v>229.74</v>
@@ -10683,7 +10683,7 @@
         <v>2.86</v>
       </c>
       <c r="B446" t="n">
-        <v>6.1541111</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="C446" t="n">
         <v>195.87</v>
@@ -10706,7 +10706,7 @@
         <v>1.93</v>
       </c>
       <c r="B447" t="n">
-        <v>6.1541111</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="C447" t="n">
         <v>129.27</v>
@@ -10729,7 +10729,7 @@
         <v>1.45</v>
       </c>
       <c r="B448" t="n">
-        <v>6.1541111</v>
+        <v>98.38</v>
       </c>
       <c r="C448" t="n">
         <v>334.46</v>
@@ -10752,7 +10752,7 @@
         <v>0.83</v>
       </c>
       <c r="B449" t="n">
-        <v>6.1541111</v>
+        <v>81.59</v>
       </c>
       <c r="C449" t="n">
         <v>168.42</v>
@@ -10775,7 +10775,7 @@
         <v>2.4</v>
       </c>
       <c r="B450" t="n">
-        <v>6.1541111</v>
+        <v>98.95</v>
       </c>
       <c r="C450" t="n">
         <v>85.45</v>
@@ -10798,7 +10798,7 @@
         <v>2.11</v>
       </c>
       <c r="B451" t="n">
-        <v>6.1541111</v>
+        <v>90.17</v>
       </c>
       <c r="C451" t="n">
         <v>190.71</v>
@@ -10821,7 +10821,7 @@
         <v>3.33</v>
       </c>
       <c r="B452" t="n">
-        <v>6.1541111</v>
+        <v>84</v>
       </c>
       <c r="C452" t="n">
         <v>175.17</v>
@@ -10844,7 +10844,7 @@
         <v>2.55</v>
       </c>
       <c r="B453" t="n">
-        <v>6.1541111</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="C453" t="n">
         <v>146.56</v>
@@ -10867,7 +10867,7 @@
         <v>0.5</v>
       </c>
       <c r="B454" t="n">
-        <v>6.1541111</v>
+        <v>108.98</v>
       </c>
       <c r="C454" t="n">
         <v>167.32</v>
@@ -10890,7 +10890,7 @@
         <v>2.78</v>
       </c>
       <c r="B455" t="n">
-        <v>6.1541111</v>
+        <v>110.01</v>
       </c>
       <c r="C455" t="n">
         <v>167.04</v>
@@ -10913,7 +10913,7 @@
         <v>2.79</v>
       </c>
       <c r="B456" t="n">
-        <v>6.1541111</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="C456" t="n">
         <v>82.52</v>
@@ -10936,7 +10936,7 @@
         <v>2.78</v>
       </c>
       <c r="B457" t="n">
-        <v>6.1541111</v>
+        <v>87.48999999999999</v>
       </c>
       <c r="C457" t="n">
         <v>106.29</v>
@@ -10959,7 +10959,7 @@
         <v>1.04</v>
       </c>
       <c r="B458" t="n">
-        <v>6.1541111</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="C458" t="n">
         <v>214.7</v>
@@ -10982,7 +10982,7 @@
         <v>0.5</v>
       </c>
       <c r="B459" t="n">
-        <v>6.1541111</v>
+        <v>75.42</v>
       </c>
       <c r="C459" t="n">
         <v>161.21</v>
@@ -11005,7 +11005,7 @@
         <v>2.09</v>
       </c>
       <c r="B460" t="n">
-        <v>6.1541111</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="C460" t="n">
         <v>176.73</v>
@@ -11028,7 +11028,7 @@
         <v>2.24</v>
       </c>
       <c r="B461" t="n">
-        <v>6.1541111</v>
+        <v>85.27000000000001</v>
       </c>
       <c r="C461" t="n">
         <v>146.62</v>
@@ -11051,7 +11051,7 @@
         <v>3.36</v>
       </c>
       <c r="B462" t="n">
-        <v>6.1541111</v>
+        <v>89.34</v>
       </c>
       <c r="C462" t="n">
         <v>117.93</v>
@@ -11074,7 +11074,7 @@
         <v>3.67</v>
       </c>
       <c r="B463" t="n">
-        <v>6.1541111</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="C463" t="n">
         <v>183.23</v>
@@ -11097,7 +11097,7 @@
         <v>2.25</v>
       </c>
       <c r="B464" t="n">
-        <v>6.1541111</v>
+        <v>66.5</v>
       </c>
       <c r="C464" t="n">
         <v>117.85</v>
@@ -11120,7 +11120,7 @@
         <v>3.9</v>
       </c>
       <c r="B465" t="n">
-        <v>6.1541111</v>
+        <v>60.7</v>
       </c>
       <c r="C465" t="n">
         <v>156.39</v>
@@ -11143,7 +11143,7 @@
         <v>2.4</v>
       </c>
       <c r="B466" t="n">
-        <v>6.1541111</v>
+        <v>72.16</v>
       </c>
       <c r="C466" t="n">
         <v>246.36</v>
@@ -11166,7 +11166,7 @@
         <v>3.3</v>
       </c>
       <c r="B467" t="n">
-        <v>6.1541111</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="C467" t="n">
         <v>121.16</v>
@@ -11189,7 +11189,7 @@
         <v>3.48</v>
       </c>
       <c r="B468" t="n">
-        <v>6.1541111</v>
+        <v>82.05</v>
       </c>
       <c r="C468" t="n">
         <v>204.79</v>
@@ -11212,7 +11212,7 @@
         <v>2</v>
       </c>
       <c r="B469" t="n">
-        <v>6.1541111</v>
+        <v>108.82</v>
       </c>
       <c r="C469" t="n">
         <v>165.14</v>
@@ -11235,7 +11235,7 @@
         <v>0.5</v>
       </c>
       <c r="B470" t="n">
-        <v>6.1541111</v>
+        <v>98.84</v>
       </c>
       <c r="C470" t="n">
         <v>160.45</v>
@@ -11258,7 +11258,7 @@
         <v>3.51</v>
       </c>
       <c r="B471" t="n">
-        <v>6.1541111</v>
+        <v>74.03</v>
       </c>
       <c r="C471" t="n">
         <v>221.05</v>
@@ -11281,7 +11281,7 @@
         <v>0.5</v>
       </c>
       <c r="B472" t="n">
-        <v>6.1541111</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="C472" t="n">
         <v>125.48</v>
@@ -11304,7 +11304,7 @@
         <v>3.06</v>
       </c>
       <c r="B473" t="n">
-        <v>6.1541111</v>
+        <v>80.69</v>
       </c>
       <c r="C473" t="n">
         <v>93.23999999999999</v>
@@ -11327,7 +11327,7 @@
         <v>1.67</v>
       </c>
       <c r="B474" t="n">
-        <v>6.1541111</v>
+        <v>82.16</v>
       </c>
       <c r="C474" t="n">
         <v>118.87</v>
@@ -11350,7 +11350,7 @@
         <v>0.55</v>
       </c>
       <c r="B475" t="n">
-        <v>6.1541111</v>
+        <v>87.8</v>
       </c>
       <c r="C475" t="n">
         <v>103.11</v>
@@ -11373,7 +11373,7 @@
         <v>3.86</v>
       </c>
       <c r="B476" t="n">
-        <v>6.1541111</v>
+        <v>93</v>
       </c>
       <c r="C476" t="n">
         <v>163.02</v>
@@ -11396,7 +11396,7 @@
         <v>1.3</v>
       </c>
       <c r="B477" t="n">
-        <v>6.1541111</v>
+        <v>81.5</v>
       </c>
       <c r="C477" t="n">
         <v>99.44</v>
@@ -11419,7 +11419,7 @@
         <v>1.58</v>
       </c>
       <c r="B478" t="n">
-        <v>6.1541111</v>
+        <v>98.34</v>
       </c>
       <c r="C478" t="n">
         <v>120.51</v>
@@ -11442,7 +11442,7 @@
         <v>1.15</v>
       </c>
       <c r="B479" t="n">
-        <v>6.1541111</v>
+        <v>71.87</v>
       </c>
       <c r="C479" t="n">
         <v>126.22</v>
@@ -11465,7 +11465,7 @@
         <v>4.09</v>
       </c>
       <c r="B480" t="n">
-        <v>6.1541111</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="C480" t="n">
         <v>292.39</v>
@@ -11488,7 +11488,7 @@
         <v>3.65</v>
       </c>
       <c r="B481" t="n">
-        <v>6.1541111</v>
+        <v>110.01</v>
       </c>
       <c r="C481" t="n">
         <v>130.42</v>
@@ -11511,7 +11511,7 @@
         <v>2.08</v>
       </c>
       <c r="B482" t="n">
-        <v>6.1541111</v>
+        <v>88.25</v>
       </c>
       <c r="C482" t="n">
         <v>169.46</v>
@@ -11534,7 +11534,7 @@
         <v>3.87</v>
       </c>
       <c r="B483" t="n">
-        <v>6.1541111</v>
+        <v>102.77</v>
       </c>
       <c r="C483" t="n">
         <v>218.79</v>
@@ -11557,7 +11557,7 @@
         <v>3.31</v>
       </c>
       <c r="B484" t="n">
-        <v>6.1541111</v>
+        <v>86.67</v>
       </c>
       <c r="C484" t="n">
         <v>116.76</v>
@@ -11580,7 +11580,7 @@
         <v>2.93</v>
       </c>
       <c r="B485" t="n">
-        <v>6.1541111</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="C485" t="n">
         <v>101.8</v>
@@ -11603,7 +11603,7 @@
         <v>3.5</v>
       </c>
       <c r="B486" t="n">
-        <v>6.1541111</v>
+        <v>84.89</v>
       </c>
       <c r="C486" t="n">
         <v>101.08</v>
@@ -11626,7 +11626,7 @@
         <v>1.35</v>
       </c>
       <c r="B487" t="n">
-        <v>6.1541111</v>
+        <v>83.53</v>
       </c>
       <c r="C487" t="n">
         <v>168.75</v>
@@ -11649,7 +11649,7 @@
         <v>0.88</v>
       </c>
       <c r="B488" t="n">
-        <v>6.1541111</v>
+        <v>76.22</v>
       </c>
       <c r="C488" t="n">
         <v>210.72</v>
@@ -11672,7 +11672,7 @@
         <v>2.63</v>
       </c>
       <c r="B489" t="n">
-        <v>6.1541111</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="C489" t="n">
         <v>312.4</v>
@@ -11695,7 +11695,7 @@
         <v>2.04</v>
       </c>
       <c r="B490" t="n">
-        <v>6.1541111</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="C490" t="n">
         <v>242.28</v>
@@ -11718,7 +11718,7 @@
         <v>3</v>
       </c>
       <c r="B491" t="n">
-        <v>6.1541111</v>
+        <v>93.56</v>
       </c>
       <c r="C491" t="n">
         <v>84.09</v>
@@ -11741,7 +11741,7 @@
         <v>2.65</v>
       </c>
       <c r="B492" t="n">
-        <v>6.1541111</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="C492" t="n">
         <v>135.26</v>
@@ -11764,7 +11764,7 @@
         <v>2.88</v>
       </c>
       <c r="B493" t="n">
-        <v>6.1541111</v>
+        <v>89.97</v>
       </c>
       <c r="C493" t="n">
         <v>43.51</v>
@@ -11787,7 +11787,7 @@
         <v>4.21</v>
       </c>
       <c r="B494" t="n">
-        <v>6.1541111</v>
+        <v>82.14</v>
       </c>
       <c r="C494" t="n">
         <v>164.91</v>
@@ -11810,7 +11810,7 @@
         <v>0.85</v>
       </c>
       <c r="B495" t="n">
-        <v>6.1541111</v>
+        <v>91.02</v>
       </c>
       <c r="C495" t="n">
         <v>98.84</v>
@@ -11833,7 +11833,7 @@
         <v>1.49</v>
       </c>
       <c r="B496" t="n">
-        <v>6.1541111</v>
+        <v>81.87</v>
       </c>
       <c r="C496" t="n">
         <v>139.49</v>
@@ -11856,7 +11856,7 @@
         <v>2.3</v>
       </c>
       <c r="B497" t="n">
-        <v>6.1541111</v>
+        <v>96.8</v>
       </c>
       <c r="C497" t="n">
         <v>165.58</v>
@@ -11879,7 +11879,7 @@
         <v>1.14</v>
       </c>
       <c r="B498" t="n">
-        <v>6.1541111</v>
+        <v>63.59</v>
       </c>
       <c r="C498" t="n">
         <v>147.83</v>
@@ -11902,7 +11902,7 @@
         <v>4.19</v>
       </c>
       <c r="B499" t="n">
-        <v>6.1541111</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="C499" t="n">
         <v>347.37</v>
@@ -11925,7 +11925,7 @@
         <v>1.5</v>
       </c>
       <c r="B500" t="n">
-        <v>6.1541111</v>
+        <v>61.68</v>
       </c>
       <c r="C500" t="n">
         <v>235.69</v>
@@ -11948,7 +11948,7 @@
         <v>2.31</v>
       </c>
       <c r="B501" t="n">
-        <v>6.1541111</v>
+        <v>67.63</v>
       </c>
       <c r="C501" t="n">
         <v>460.8</v>
@@ -11971,7 +11971,7 @@
         <v>3.17</v>
       </c>
       <c r="B502" t="n">
-        <v>6.1541111</v>
+        <v>101.94</v>
       </c>
       <c r="C502" t="n">
         <v>149.91</v>
@@ -11994,7 +11994,7 @@
         <v>1.09</v>
       </c>
       <c r="B503" t="n">
-        <v>6.1541111</v>
+        <v>96.31</v>
       </c>
       <c r="C503" t="n">
         <v>245.25</v>
@@ -12017,7 +12017,7 @@
         <v>3.54</v>
       </c>
       <c r="B504" t="n">
-        <v>6.1541111</v>
+        <v>76.94</v>
       </c>
       <c r="C504" t="n">
         <v>208.97</v>
@@ -12040,7 +12040,7 @@
         <v>1.6</v>
       </c>
       <c r="B505" t="n">
-        <v>6.1541111</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="C505" t="n">
         <v>199.1</v>
@@ -12063,7 +12063,7 @@
         <v>1.4</v>
       </c>
       <c r="B506" t="n">
-        <v>6.1541111</v>
+        <v>60.37</v>
       </c>
       <c r="C506" t="n">
         <v>443.5</v>
@@ -12086,7 +12086,7 @@
         <v>2.76</v>
       </c>
       <c r="B507" t="n">
-        <v>6.1541111</v>
+        <v>79.05</v>
       </c>
       <c r="C507" t="n">
         <v>215.64</v>
@@ -12109,7 +12109,7 @@
         <v>3.14</v>
       </c>
       <c r="B508" t="n">
-        <v>6.1541111</v>
+        <v>110.01</v>
       </c>
       <c r="C508" t="n">
         <v>107.27</v>
@@ -12132,7 +12132,7 @@
         <v>3.7</v>
       </c>
       <c r="B509" t="n">
-        <v>6.1541111</v>
+        <v>90.79000000000001</v>
       </c>
       <c r="C509" t="n">
         <v>112.9</v>
@@ -12155,7 +12155,7 @@
         <v>2.92</v>
       </c>
       <c r="B510" t="n">
-        <v>6.1541111</v>
+        <v>78.86</v>
       </c>
       <c r="C510" t="n">
         <v>130.07</v>
@@ -12178,7 +12178,7 @@
         <v>3.21</v>
       </c>
       <c r="B511" t="n">
-        <v>6.1541111</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="C511" t="n">
         <v>49.44</v>
@@ -12201,7 +12201,7 @@
         <v>2.9</v>
       </c>
       <c r="B512" t="n">
-        <v>6.1541111</v>
+        <v>66.84</v>
       </c>
       <c r="C512" t="n">
         <v>285.81</v>
@@ -12224,7 +12224,7 @@
         <v>1.55</v>
       </c>
       <c r="B513" t="n">
-        <v>6.1541111</v>
+        <v>82</v>
       </c>
       <c r="C513" t="n">
         <v>144.56</v>
@@ -12247,7 +12247,7 @@
         <v>1.76</v>
       </c>
       <c r="B514" t="n">
-        <v>6.1541111</v>
+        <v>86.77</v>
       </c>
       <c r="C514" t="n">
         <v>294.03</v>
@@ -12270,7 +12270,7 @@
         <v>3.21</v>
       </c>
       <c r="B515" t="n">
-        <v>6.1541111</v>
+        <v>84.54000000000001</v>
       </c>
       <c r="C515" t="n">
         <v>156.89</v>
@@ -12293,7 +12293,7 @@
         <v>3.89</v>
       </c>
       <c r="B516" t="n">
-        <v>6.1541111</v>
+        <v>95.06</v>
       </c>
       <c r="C516" t="n">
         <v>184</v>
@@ -12316,7 +12316,7 @@
         <v>2.18</v>
       </c>
       <c r="B517" t="n">
-        <v>6.1541111</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="C517" t="n">
         <v>243.65</v>
@@ -12339,7 +12339,7 @@
         <v>0.5</v>
       </c>
       <c r="B518" t="n">
-        <v>6.1541111</v>
+        <v>93.59</v>
       </c>
       <c r="C518" t="n">
         <v>141.81</v>
@@ -12362,7 +12362,7 @@
         <v>0.5</v>
       </c>
       <c r="B519" t="n">
-        <v>6.1541111</v>
+        <v>77.31</v>
       </c>
       <c r="C519" t="n">
         <v>180.39</v>
@@ -12385,7 +12385,7 @@
         <v>2.71</v>
       </c>
       <c r="B520" t="n">
-        <v>6.1541111</v>
+        <v>96.34999999999999</v>
       </c>
       <c r="C520" t="n">
         <v>147.09</v>
@@ -12408,7 +12408,7 @@
         <v>3.52</v>
       </c>
       <c r="B521" t="n">
-        <v>6.1541111</v>
+        <v>105.12</v>
       </c>
       <c r="C521" t="n">
         <v>145.51</v>
@@ -12431,7 +12431,7 @@
         <v>3.14</v>
       </c>
       <c r="B522" t="n">
-        <v>6.1541111</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="C522" t="n">
         <v>43.86</v>
@@ -12454,7 +12454,7 @@
         <v>2.88</v>
       </c>
       <c r="B523" t="n">
-        <v>6.1541111</v>
+        <v>74.92</v>
       </c>
       <c r="C523" t="n">
         <v>85.48999999999999</v>
@@ -12477,7 +12477,7 @@
         <v>3.61</v>
       </c>
       <c r="B524" t="n">
-        <v>6.1541111</v>
+        <v>101.6</v>
       </c>
       <c r="C524" t="n">
         <v>171.31</v>
@@ -12500,7 +12500,7 @@
         <v>2.58</v>
       </c>
       <c r="B525" t="n">
-        <v>6.1541111</v>
+        <v>83.28</v>
       </c>
       <c r="C525" t="n">
         <v>93.23999999999999</v>
@@ -12523,7 +12523,7 @@
         <v>1.91</v>
       </c>
       <c r="B526" t="n">
-        <v>6.1541111</v>
+        <v>102.42</v>
       </c>
       <c r="C526" t="n">
         <v>130.93</v>
@@ -12546,7 +12546,7 @@
         <v>2.37</v>
       </c>
       <c r="B527" t="n">
-        <v>6.1541111</v>
+        <v>80.26000000000001</v>
       </c>
       <c r="C527" t="n">
         <v>222.29</v>
@@ -12569,7 +12569,7 @@
         <v>2.79</v>
       </c>
       <c r="B528" t="n">
-        <v>6.1541111</v>
+        <v>103.03</v>
       </c>
       <c r="C528" t="n">
         <v>123.31</v>
@@ -12592,7 +12592,7 @@
         <v>2.97</v>
       </c>
       <c r="B529" t="n">
-        <v>6.1541111</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="C529" t="n">
         <v>125.56</v>
@@ -12615,7 +12615,7 @@
         <v>0.5</v>
       </c>
       <c r="B530" t="n">
-        <v>6.1541111</v>
+        <v>88.67</v>
       </c>
       <c r="C530" t="n">
         <v>153.44</v>
@@ -12638,7 +12638,7 @@
         <v>2.89</v>
       </c>
       <c r="B531" t="n">
-        <v>6.1541111</v>
+        <v>104.35</v>
       </c>
       <c r="C531" t="n">
         <v>220.79</v>
@@ -12661,7 +12661,7 @@
         <v>2.15</v>
       </c>
       <c r="B532" t="n">
-        <v>6.1541111</v>
+        <v>81.23</v>
       </c>
       <c r="C532" t="n">
         <v>99.41</v>
@@ -12684,7 +12684,7 @@
         <v>2.65</v>
       </c>
       <c r="B533" t="n">
-        <v>6.1541111</v>
+        <v>74.28</v>
       </c>
       <c r="C533" t="n">
         <v>275.78</v>
@@ -12707,7 +12707,7 @@
         <v>2.47</v>
       </c>
       <c r="B534" t="n">
-        <v>6.1541111</v>
+        <v>80.19</v>
       </c>
       <c r="C534" t="n">
         <v>240.81</v>
@@ -12730,7 +12730,7 @@
         <v>2.59</v>
       </c>
       <c r="B535" t="n">
-        <v>6.1541111</v>
+        <v>91</v>
       </c>
       <c r="C535" t="n">
         <v>289.48</v>
@@ -12753,7 +12753,7 @@
         <v>1.54</v>
       </c>
       <c r="B536" t="n">
-        <v>6.1541111</v>
+        <v>66.78</v>
       </c>
       <c r="C536" t="n">
         <v>155.98</v>
@@ -12776,7 +12776,7 @@
         <v>1.94</v>
       </c>
       <c r="B537" t="n">
-        <v>6.1541111</v>
+        <v>93.22</v>
       </c>
       <c r="C537" t="n">
         <v>158.76</v>
@@ -12799,7 +12799,7 @@
         <v>1.59</v>
       </c>
       <c r="B538" t="n">
-        <v>6.1541111</v>
+        <v>79.11</v>
       </c>
       <c r="C538" t="n">
         <v>120.69</v>
@@ -12822,7 +12822,7 @@
         <v>1.77</v>
       </c>
       <c r="B539" t="n">
-        <v>6.1541111</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="C539" t="n">
         <v>159.16</v>
@@ -12845,7 +12845,7 @@
         <v>1.14</v>
       </c>
       <c r="B540" t="n">
-        <v>6.1541111</v>
+        <v>60.37</v>
       </c>
       <c r="C540" t="n">
         <v>123.95</v>
@@ -12868,7 +12868,7 @@
         <v>1.52</v>
       </c>
       <c r="B541" t="n">
-        <v>6.1541111</v>
+        <v>76.13</v>
       </c>
       <c r="C541" t="n">
         <v>139.1</v>
@@ -12891,7 +12891,7 @@
         <v>3.55</v>
       </c>
       <c r="B542" t="n">
-        <v>6.1541111</v>
+        <v>65.33</v>
       </c>
       <c r="C542" t="n">
         <v>360.42</v>
@@ -12914,7 +12914,7 @@
         <v>2.83</v>
       </c>
       <c r="B543" t="n">
-        <v>6.1541111</v>
+        <v>75.66</v>
       </c>
       <c r="C543" t="n">
         <v>153.82</v>
@@ -12937,7 +12937,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="B544" t="n">
-        <v>6.1541111</v>
+        <v>88.54000000000001</v>
       </c>
       <c r="C544" t="n">
         <v>191.33</v>
@@ -12960,7 +12960,7 @@
         <v>1.05</v>
       </c>
       <c r="B545" t="n">
-        <v>6.1541111</v>
+        <v>83.42</v>
       </c>
       <c r="C545" t="n">
         <v>427.71</v>
@@ -12983,7 +12983,7 @@
         <v>0.5</v>
       </c>
       <c r="B546" t="n">
-        <v>6.1541111</v>
+        <v>82.53</v>
       </c>
       <c r="C546" t="n">
         <v>188.52</v>
@@ -13006,7 +13006,7 @@
         <v>0.71</v>
       </c>
       <c r="B547" t="n">
-        <v>6.1541111</v>
+        <v>83.66</v>
       </c>
       <c r="C547" t="n">
         <v>109.71</v>
@@ -13029,7 +13029,7 @@
         <v>1.65</v>
       </c>
       <c r="B548" t="n">
-        <v>6.1541111</v>
+        <v>88.01000000000001</v>
       </c>
       <c r="C548" t="n">
         <v>197.83</v>
@@ -13052,7 +13052,7 @@
         <v>0.5</v>
       </c>
       <c r="B549" t="n">
-        <v>6.1541111</v>
+        <v>73.47</v>
       </c>
       <c r="C549" t="n">
         <v>254.11</v>
@@ -13075,7 +13075,7 @@
         <v>3.44</v>
       </c>
       <c r="B550" t="n">
-        <v>6.1541111</v>
+        <v>94.05</v>
       </c>
       <c r="C550" t="n">
         <v>124.18</v>
@@ -13098,7 +13098,7 @@
         <v>2.35</v>
       </c>
       <c r="B551" t="n">
-        <v>6.1541111</v>
+        <v>93.52</v>
       </c>
       <c r="C551" t="n">
         <v>174.15</v>
@@ -13121,7 +13121,7 @@
         <v>3</v>
       </c>
       <c r="B552" t="n">
-        <v>6.1541111</v>
+        <v>90.19</v>
       </c>
       <c r="C552" t="n">
         <v>134.03</v>
@@ -13144,7 +13144,7 @@
         <v>4.42</v>
       </c>
       <c r="B553" t="n">
-        <v>6.1541111</v>
+        <v>92.25</v>
       </c>
       <c r="C553" t="n">
         <v>88.73</v>
@@ -13167,7 +13167,7 @@
         <v>2.15</v>
       </c>
       <c r="B554" t="n">
-        <v>6.1541111</v>
+        <v>89.13</v>
       </c>
       <c r="C554" t="n">
         <v>219.98</v>
@@ -13190,7 +13190,7 @@
         <v>0.74</v>
       </c>
       <c r="B555" t="n">
-        <v>6.1541111</v>
+        <v>109.99</v>
       </c>
       <c r="C555" t="n">
         <v>216.02</v>
@@ -13213,7 +13213,7 @@
         <v>3.72</v>
       </c>
       <c r="B556" t="n">
-        <v>6.1541111</v>
+        <v>84.53</v>
       </c>
       <c r="C556" t="n">
         <v>108.29</v>
@@ -13236,7 +13236,7 @@
         <v>0.63</v>
       </c>
       <c r="B557" t="n">
-        <v>6.1541111</v>
+        <v>81.89</v>
       </c>
       <c r="C557" t="n">
         <v>188</v>
@@ -13259,7 +13259,7 @@
         <v>3.38</v>
       </c>
       <c r="B558" t="n">
-        <v>6.1541111</v>
+        <v>76.53</v>
       </c>
       <c r="C558" t="n">
         <v>204.41</v>
@@ -13282,7 +13282,7 @@
         <v>0.65</v>
       </c>
       <c r="B559" t="n">
-        <v>6.1541111</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="C559" t="n">
         <v>177.7</v>
@@ -13305,7 +13305,7 @@
         <v>1.54</v>
       </c>
       <c r="B560" t="n">
-        <v>6.1541111</v>
+        <v>70.64</v>
       </c>
       <c r="C560" t="n">
         <v>122.69</v>
@@ -13328,7 +13328,7 @@
         <v>1.14</v>
       </c>
       <c r="B561" t="n">
-        <v>6.1541111</v>
+        <v>74.91</v>
       </c>
       <c r="C561" t="n">
         <v>157.83</v>
@@ -13351,7 +13351,7 @@
         <v>3.02</v>
       </c>
       <c r="B562" t="n">
-        <v>6.1541111</v>
+        <v>84.72</v>
       </c>
       <c r="C562" t="n">
         <v>145.52</v>
@@ -13374,7 +13374,7 @@
         <v>1.17</v>
       </c>
       <c r="B563" t="n">
-        <v>6.1541111</v>
+        <v>89.58</v>
       </c>
       <c r="C563" t="n">
         <v>151.04</v>
@@ -13397,7 +13397,7 @@
         <v>1.61</v>
       </c>
       <c r="B564" t="n">
-        <v>6.1541111</v>
+        <v>86.19</v>
       </c>
       <c r="C564" t="n">
         <v>168.33</v>
@@ -13420,7 +13420,7 @@
         <v>1.99</v>
       </c>
       <c r="B565" t="n">
-        <v>6.1541111</v>
+        <v>76.39</v>
       </c>
       <c r="C565" t="n">
         <v>278.6</v>
@@ -13443,7 +13443,7 @@
         <v>2.72</v>
       </c>
       <c r="B566" t="n">
-        <v>6.1541111</v>
+        <v>96.37</v>
       </c>
       <c r="C566" t="n">
         <v>74.08</v>
@@ -13466,7 +13466,7 @@
         <v>3.6</v>
       </c>
       <c r="B567" t="n">
-        <v>6.1541111</v>
+        <v>94.44</v>
       </c>
       <c r="C567" t="n">
         <v>87.58</v>
@@ -13489,7 +13489,7 @@
         <v>4.08</v>
       </c>
       <c r="B568" t="n">
-        <v>6.1541111</v>
+        <v>83.66</v>
       </c>
       <c r="C568" t="n">
         <v>463.21</v>
@@ -13512,7 +13512,7 @@
         <v>2.42</v>
       </c>
       <c r="B569" t="n">
-        <v>6.1541111</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="C569" t="n">
         <v>60.61</v>
@@ -13535,7 +13535,7 @@
         <v>0.75</v>
       </c>
       <c r="B570" t="n">
-        <v>6.1541111</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="C570" t="n">
         <v>271.49</v>
@@ -13558,7 +13558,7 @@
         <v>1.25</v>
       </c>
       <c r="B571" t="n">
-        <v>6.1541111</v>
+        <v>87.83</v>
       </c>
       <c r="C571" t="n">
         <v>179.93</v>
@@ -13581,7 +13581,7 @@
         <v>2.12</v>
       </c>
       <c r="B572" t="n">
-        <v>6.1541111</v>
+        <v>68.19</v>
       </c>
       <c r="C572" t="n">
         <v>224.07</v>
@@ -13604,7 +13604,7 @@
         <v>1.6</v>
       </c>
       <c r="B573" t="n">
-        <v>6.1541111</v>
+        <v>84.76000000000001</v>
       </c>
       <c r="C573" t="n">
         <v>303.34</v>
@@ -13627,7 +13627,7 @@
         <v>1.16</v>
       </c>
       <c r="B574" t="n">
-        <v>6.1541111</v>
+        <v>88.72</v>
       </c>
       <c r="C574" t="n">
         <v>120.53</v>
@@ -13650,7 +13650,7 @@
         <v>1.23</v>
       </c>
       <c r="B575" t="n">
-        <v>6.1541111</v>
+        <v>74.78</v>
       </c>
       <c r="C575" t="n">
         <v>98.09</v>
@@ -13673,7 +13673,7 @@
         <v>1.82</v>
       </c>
       <c r="B576" t="n">
-        <v>6.1541111</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="C576" t="n">
         <v>347.32</v>
@@ -13696,7 +13696,7 @@
         <v>1.26</v>
       </c>
       <c r="B577" t="n">
-        <v>6.1541111</v>
+        <v>68.11</v>
       </c>
       <c r="C577" t="n">
         <v>104.25</v>
@@ -13719,7 +13719,7 @@
         <v>0.77</v>
       </c>
       <c r="B578" t="n">
-        <v>6.1541111</v>
+        <v>101.61</v>
       </c>
       <c r="C578" t="n">
         <v>226.48</v>
@@ -13742,7 +13742,7 @@
         <v>2.91</v>
       </c>
       <c r="B579" t="n">
-        <v>6.1541111</v>
+        <v>100.55</v>
       </c>
       <c r="C579" t="n">
         <v>118.41</v>
@@ -13765,7 +13765,7 @@
         <v>2.13</v>
       </c>
       <c r="B580" t="n">
-        <v>6.1541111</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="C580" t="n">
         <v>129.4</v>
@@ -13788,7 +13788,7 @@
         <v>4.21</v>
       </c>
       <c r="B581" t="n">
-        <v>6.1541111</v>
+        <v>89.93000000000001</v>
       </c>
       <c r="C581" t="n">
         <v>105.65</v>
@@ -13811,7 +13811,7 @@
         <v>3.05</v>
       </c>
       <c r="B582" t="n">
-        <v>6.1541111</v>
+        <v>60.37</v>
       </c>
       <c r="C582" t="n">
         <v>176.5</v>
@@ -13834,7 +13834,7 @@
         <v>1.15</v>
       </c>
       <c r="B583" t="n">
-        <v>6.1541111</v>
+        <v>71.7</v>
       </c>
       <c r="C583" t="n">
         <v>135.97</v>
@@ -13857,7 +13857,7 @@
         <v>2.03</v>
       </c>
       <c r="B584" t="n">
-        <v>6.1541111</v>
+        <v>82.05</v>
       </c>
       <c r="C584" t="n">
         <v>189.2</v>
@@ -13880,7 +13880,7 @@
         <v>1.62</v>
       </c>
       <c r="B585" t="n">
-        <v>6.1541111</v>
+        <v>72.70999999999999</v>
       </c>
       <c r="C585" t="n">
         <v>247.37</v>
@@ -13903,7 +13903,7 @@
         <v>1.82</v>
       </c>
       <c r="B586" t="n">
-        <v>6.1541111</v>
+        <v>94.14</v>
       </c>
       <c r="C586" t="n">
         <v>397.64</v>
@@ -13926,7 +13926,7 @@
         <v>1.08</v>
       </c>
       <c r="B587" t="n">
-        <v>6.1541111</v>
+        <v>109.54</v>
       </c>
       <c r="C587" t="n">
         <v>351.76</v>
@@ -13949,7 +13949,7 @@
         <v>4.77</v>
       </c>
       <c r="B588" t="n">
-        <v>6.1541111</v>
+        <v>71.45</v>
       </c>
       <c r="C588" t="n">
         <v>271.06</v>
@@ -13972,7 +13972,7 @@
         <v>2.11</v>
       </c>
       <c r="B589" t="n">
-        <v>6.1541111</v>
+        <v>75.52</v>
       </c>
       <c r="C589" t="n">
         <v>127.56</v>
@@ -13995,7 +13995,7 @@
         <v>3.71</v>
       </c>
       <c r="B590" t="n">
-        <v>6.1541111</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="C590" t="n">
         <v>104.41</v>
@@ -14018,7 +14018,7 @@
         <v>2.11</v>
       </c>
       <c r="B591" t="n">
-        <v>6.1541111</v>
+        <v>104.91</v>
       </c>
       <c r="C591" t="n">
         <v>126.22</v>
@@ -14041,7 +14041,7 @@
         <v>3.17</v>
       </c>
       <c r="B592" t="n">
-        <v>6.1541111</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="C592" t="n">
         <v>156.66</v>
@@ -14064,7 +14064,7 @@
         <v>1.82</v>
       </c>
       <c r="B593" t="n">
-        <v>6.1541111</v>
+        <v>88.56</v>
       </c>
       <c r="C593" t="n">
         <v>200.21</v>
@@ -14087,7 +14087,7 @@
         <v>1.99</v>
       </c>
       <c r="B594" t="n">
-        <v>6.1541111</v>
+        <v>107.43</v>
       </c>
       <c r="C594" t="n">
         <v>143.53</v>
@@ -14110,7 +14110,7 @@
         <v>0.98</v>
       </c>
       <c r="B595" t="n">
-        <v>6.1541111</v>
+        <v>65.75</v>
       </c>
       <c r="C595" t="n">
         <v>358.26</v>
@@ -14133,7 +14133,7 @@
         <v>2.6</v>
       </c>
       <c r="B596" t="n">
-        <v>6.1541111</v>
+        <v>70.2</v>
       </c>
       <c r="C596" t="n">
         <v>190.65</v>
@@ -14156,7 +14156,7 @@
         <v>1.31</v>
       </c>
       <c r="B597" t="n">
-        <v>6.1541111</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="C597" t="n">
         <v>204.3</v>
@@ -14179,7 +14179,7 @@
         <v>2.47</v>
       </c>
       <c r="B598" t="n">
-        <v>6.1541111</v>
+        <v>79.31999999999999</v>
       </c>
       <c r="C598" t="n">
         <v>217.57</v>
@@ -14202,7 +14202,7 @@
         <v>2.18</v>
       </c>
       <c r="B599" t="n">
-        <v>6.1541111</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="C599" t="n">
         <v>279.38</v>
@@ -14225,7 +14225,7 @@
         <v>3.31</v>
       </c>
       <c r="B600" t="n">
-        <v>6.1541111</v>
+        <v>88.47</v>
       </c>
       <c r="C600" t="n">
         <v>201.28</v>
@@ -14248,7 +14248,7 @@
         <v>4.56</v>
       </c>
       <c r="B601" t="n">
-        <v>6.1541111</v>
+        <v>64.27</v>
       </c>
       <c r="C601" t="n">
         <v>40</v>
@@ -14271,7 +14271,7 @@
         <v>2.98</v>
       </c>
       <c r="B602" t="n">
-        <v>6.1541111</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="C602" t="n">
         <v>139.63</v>
@@ -14294,7 +14294,7 @@
         <v>4.2</v>
       </c>
       <c r="B603" t="n">
-        <v>6.1541111</v>
+        <v>78.64</v>
       </c>
       <c r="C603" t="n">
         <v>215.58</v>
@@ -14317,7 +14317,7 @@
         <v>4.1</v>
       </c>
       <c r="B604" t="n">
-        <v>6.1541111</v>
+        <v>100.87</v>
       </c>
       <c r="C604" t="n">
         <v>274.99</v>
@@ -14340,7 +14340,7 @@
         <v>4.38</v>
       </c>
       <c r="B605" t="n">
-        <v>6.1541111</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="C605" t="n">
         <v>114.55</v>
@@ -14363,7 +14363,7 @@
         <v>5</v>
       </c>
       <c r="B606" t="n">
-        <v>6.1541111</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="C606" t="n">
         <v>157.21</v>
@@ -14386,7 +14386,7 @@
         <v>4.42</v>
       </c>
       <c r="B607" t="n">
-        <v>6.1541111</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="C607" t="n">
         <v>219.79</v>
@@ -14409,7 +14409,7 @@
         <v>3.54</v>
       </c>
       <c r="B608" t="n">
-        <v>6.1541111</v>
+        <v>94.73</v>
       </c>
       <c r="C608" t="n">
         <v>186.16</v>
@@ -14432,7 +14432,7 @@
         <v>2.49</v>
       </c>
       <c r="B609" t="n">
-        <v>6.1541111</v>
+        <v>90.95</v>
       </c>
       <c r="C609" t="n">
         <v>135.61</v>
@@ -14455,7 +14455,7 @@
         <v>3.41</v>
       </c>
       <c r="B610" t="n">
-        <v>6.1541111</v>
+        <v>65.34</v>
       </c>
       <c r="C610" t="n">
         <v>127.7</v>
@@ -14478,7 +14478,7 @@
         <v>3.23</v>
       </c>
       <c r="B611" t="n">
-        <v>6.1541111</v>
+        <v>92.03</v>
       </c>
       <c r="C611" t="n">
         <v>254.17</v>
@@ -14501,7 +14501,7 @@
         <v>0.5</v>
       </c>
       <c r="B612" t="n">
-        <v>6.1541111</v>
+        <v>73.16</v>
       </c>
       <c r="C612" t="n">
         <v>169.5</v>
@@ -14524,7 +14524,7 @@
         <v>2.45</v>
       </c>
       <c r="B613" t="n">
-        <v>6.1541111</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="C613" t="n">
         <v>232.52</v>
@@ -14547,7 +14547,7 @@
         <v>0.5</v>
       </c>
       <c r="B614" t="n">
-        <v>6.1541111</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="C614" t="n">
         <v>106.52</v>
@@ -14570,7 +14570,7 @@
         <v>3.01</v>
       </c>
       <c r="B615" t="n">
-        <v>6.1541111</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="C615" t="n">
         <v>170.77</v>
@@ -14593,7 +14593,7 @@
         <v>0.97</v>
       </c>
       <c r="B616" t="n">
-        <v>6.1541111</v>
+        <v>75.89</v>
       </c>
       <c r="C616" t="n">
         <v>220.82</v>
@@ -14616,7 +14616,7 @@
         <v>0.65</v>
       </c>
       <c r="B617" t="n">
-        <v>6.1541111</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="C617" t="n">
         <v>121.61</v>
@@ -14639,7 +14639,7 @@
         <v>2.41</v>
       </c>
       <c r="B618" t="n">
-        <v>6.1541111</v>
+        <v>94.14</v>
       </c>
       <c r="C618" t="n">
         <v>138.84</v>
@@ -14662,7 +14662,7 @@
         <v>0.66</v>
       </c>
       <c r="B619" t="n">
-        <v>6.1541111</v>
+        <v>88.47</v>
       </c>
       <c r="C619" t="n">
         <v>148.1</v>
@@ -14685,7 +14685,7 @@
         <v>3.88</v>
       </c>
       <c r="B620" t="n">
-        <v>6.1541111</v>
+        <v>78.2</v>
       </c>
       <c r="C620" t="n">
         <v>212.12</v>
@@ -14708,7 +14708,7 @@
         <v>3.44</v>
       </c>
       <c r="B621" t="n">
-        <v>6.1541111</v>
+        <v>102.99</v>
       </c>
       <c r="C621" t="n">
         <v>173.01</v>
@@ -14731,7 +14731,7 @@
         <v>3.6</v>
       </c>
       <c r="B622" t="n">
-        <v>6.1541111</v>
+        <v>80.28</v>
       </c>
       <c r="C622" t="n">
         <v>57.99</v>
@@ -14754,7 +14754,7 @@
         <v>2.25</v>
       </c>
       <c r="B623" t="n">
-        <v>6.1541111</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="C623" t="n">
         <v>141.87</v>
@@ -14777,7 +14777,7 @@
         <v>1.15</v>
       </c>
       <c r="B624" t="n">
-        <v>6.1541111</v>
+        <v>88.8</v>
       </c>
       <c r="C624" t="n">
         <v>70.16</v>
@@ -14800,7 +14800,7 @@
         <v>3.67</v>
       </c>
       <c r="B625" t="n">
-        <v>6.1541111</v>
+        <v>78.14</v>
       </c>
       <c r="C625" t="n">
         <v>157.9</v>
@@ -14823,7 +14823,7 @@
         <v>2.12</v>
       </c>
       <c r="B626" t="n">
-        <v>6.1541111</v>
+        <v>91.23</v>
       </c>
       <c r="C626" t="n">
         <v>144.32</v>
@@ -14846,7 +14846,7 @@
         <v>2.39</v>
       </c>
       <c r="B627" t="n">
-        <v>6.1541111</v>
+        <v>79.17</v>
       </c>
       <c r="C627" t="n">
         <v>197.08</v>
@@ -14869,7 +14869,7 @@
         <v>3.71</v>
       </c>
       <c r="B628" t="n">
-        <v>6.1541111</v>
+        <v>80.63</v>
       </c>
       <c r="C628" t="n">
         <v>114.5</v>
@@ -14892,7 +14892,7 @@
         <v>2.21</v>
       </c>
       <c r="B629" t="n">
-        <v>6.1541111</v>
+        <v>101.92</v>
       </c>
       <c r="C629" t="n">
         <v>185.29</v>
@@ -14915,7 +14915,7 @@
         <v>2.94</v>
       </c>
       <c r="B630" t="n">
-        <v>6.1541111</v>
+        <v>73.08</v>
       </c>
       <c r="C630" t="n">
         <v>257.34</v>
@@ -14938,7 +14938,7 @@
         <v>3.8</v>
       </c>
       <c r="B631" t="n">
-        <v>6.1541111</v>
+        <v>60.37</v>
       </c>
       <c r="C631" t="n">
         <v>168.8</v>
@@ -14961,7 +14961,7 @@
         <v>1.8</v>
       </c>
       <c r="B632" t="n">
-        <v>6.1541111</v>
+        <v>104.9</v>
       </c>
       <c r="C632" t="n">
         <v>154.75</v>
@@ -14984,7 +14984,7 @@
         <v>1.84</v>
       </c>
       <c r="B633" t="n">
-        <v>6.1541111</v>
+        <v>110.01</v>
       </c>
       <c r="C633" t="n">
         <v>115.52</v>
@@ -15007,7 +15007,7 @@
         <v>1.76</v>
       </c>
       <c r="B634" t="n">
-        <v>6.1541111</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="C634" t="n">
         <v>113.41</v>
@@ -15030,7 +15030,7 @@
         <v>0.52</v>
       </c>
       <c r="B635" t="n">
-        <v>6.1541111</v>
+        <v>62.33</v>
       </c>
       <c r="C635" t="n">
         <v>128.89</v>
@@ -15053,7 +15053,7 @@
         <v>4.38</v>
       </c>
       <c r="B636" t="n">
-        <v>6.1541111</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="C636" t="n">
         <v>146.02</v>
@@ -15076,7 +15076,7 @@
         <v>0.5</v>
       </c>
       <c r="B637" t="n">
-        <v>6.1541111</v>
+        <v>82.14</v>
       </c>
       <c r="C637" t="n">
         <v>171.8</v>
@@ -15099,7 +15099,7 @@
         <v>1.02</v>
       </c>
       <c r="B638" t="n">
-        <v>6.1541111</v>
+        <v>83.29000000000001</v>
       </c>
       <c r="C638" t="n">
         <v>457.18</v>
@@ -15122,7 +15122,7 @@
         <v>1.1</v>
       </c>
       <c r="B639" t="n">
-        <v>6.1541111</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="C639" t="n">
         <v>232.47</v>
@@ -15145,7 +15145,7 @@
         <v>1.8</v>
       </c>
       <c r="B640" t="n">
-        <v>6.1541111</v>
+        <v>92.53</v>
       </c>
       <c r="C640" t="n">
         <v>49.7</v>
@@ -15168,7 +15168,7 @@
         <v>1.15</v>
       </c>
       <c r="B641" t="n">
-        <v>6.1541111</v>
+        <v>91.87</v>
       </c>
       <c r="C641" t="n">
         <v>156.61</v>
@@ -15191,7 +15191,7 @@
         <v>1.01</v>
       </c>
       <c r="B642" t="n">
-        <v>6.1541111</v>
+        <v>67.64</v>
       </c>
       <c r="C642" t="n">
         <v>146.68</v>
@@ -15214,7 +15214,7 @@
         <v>3.38</v>
       </c>
       <c r="B643" t="n">
-        <v>6.1541111</v>
+        <v>93.95999999999999</v>
       </c>
       <c r="C643" t="n">
         <v>249.34</v>
@@ -15237,7 +15237,7 @@
         <v>2.44</v>
       </c>
       <c r="B644" t="n">
-        <v>6.1541111</v>
+        <v>110.01</v>
       </c>
       <c r="C644" t="n">
         <v>66.95</v>
@@ -15260,7 +15260,7 @@
         <v>2.88</v>
       </c>
       <c r="B645" t="n">
-        <v>6.1541111</v>
+        <v>87.64</v>
       </c>
       <c r="C645" t="n">
         <v>159.3</v>
@@ -15283,7 +15283,7 @@
         <v>4.63</v>
       </c>
       <c r="B646" t="n">
-        <v>6.1541111</v>
+        <v>81.52</v>
       </c>
       <c r="C646" t="n">
         <v>355.8</v>
@@ -15306,7 +15306,7 @@
         <v>2.69</v>
       </c>
       <c r="B647" t="n">
-        <v>6.1541111</v>
+        <v>83.87</v>
       </c>
       <c r="C647" t="n">
         <v>212.49</v>
@@ -15329,7 +15329,7 @@
         <v>0.5</v>
       </c>
       <c r="B648" t="n">
-        <v>6.1541111</v>
+        <v>92.95</v>
       </c>
       <c r="C648" t="n">
         <v>97.34</v>
@@ -15352,7 +15352,7 @@
         <v>0.82</v>
       </c>
       <c r="B649" t="n">
-        <v>6.1541111</v>
+        <v>64.8</v>
       </c>
       <c r="C649" t="n">
         <v>151.92</v>
@@ -15375,7 +15375,7 @@
         <v>1.54</v>
       </c>
       <c r="B650" t="n">
-        <v>6.1541111</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="C650" t="n">
         <v>123.53</v>
@@ -15398,7 +15398,7 @@
         <v>2.76</v>
       </c>
       <c r="B651" t="n">
-        <v>6.1541111</v>
+        <v>80.89</v>
       </c>
       <c r="C651" t="n">
         <v>104.61</v>
@@ -15421,7 +15421,7 @@
         <v>2.99</v>
       </c>
       <c r="B652" t="n">
-        <v>6.1541111</v>
+        <v>107.75</v>
       </c>
       <c r="C652" t="n">
         <v>210.18</v>
@@ -15444,7 +15444,7 @@
         <v>2.52</v>
       </c>
       <c r="B653" t="n">
-        <v>6.1541111</v>
+        <v>83.48</v>
       </c>
       <c r="C653" t="n">
         <v>99.84999999999999</v>
@@ -15467,7 +15467,7 @@
         <v>1.77</v>
       </c>
       <c r="B654" t="n">
-        <v>6.1541111</v>
+        <v>105.59</v>
       </c>
       <c r="C654" t="n">
         <v>86.18000000000001</v>
@@ -15490,7 +15490,7 @@
         <v>2.52</v>
       </c>
       <c r="B655" t="n">
-        <v>6.1541111</v>
+        <v>72.33</v>
       </c>
       <c r="C655" t="n">
         <v>105.72</v>
@@ -15513,7 +15513,7 @@
         <v>3.65</v>
       </c>
       <c r="B656" t="n">
-        <v>6.1541111</v>
+        <v>92.62</v>
       </c>
       <c r="C656" t="n">
         <v>105.26</v>
@@ -15536,7 +15536,7 @@
         <v>0.5</v>
       </c>
       <c r="B657" t="n">
-        <v>6.1541111</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="C657" t="n">
         <v>229.87</v>
@@ -15559,7 +15559,7 @@
         <v>2.03</v>
       </c>
       <c r="B658" t="n">
-        <v>6.1541111</v>
+        <v>75.14</v>
       </c>
       <c r="C658" t="n">
         <v>227.72</v>
@@ -15582,7 +15582,7 @@
         <v>1.16</v>
       </c>
       <c r="B659" t="n">
-        <v>6.1541111</v>
+        <v>87.7</v>
       </c>
       <c r="C659" t="n">
         <v>201.64</v>
@@ -15605,7 +15605,7 @@
         <v>1.7</v>
       </c>
       <c r="B660" t="n">
-        <v>6.1541111</v>
+        <v>100.12</v>
       </c>
       <c r="C660" t="n">
         <v>118.2</v>
@@ -15628,7 +15628,7 @@
         <v>2.56</v>
       </c>
       <c r="B661" t="n">
-        <v>6.1541111</v>
+        <v>81.69</v>
       </c>
       <c r="C661" t="n">
         <v>71.59</v>
@@ -15651,7 +15651,7 @@
         <v>3.5</v>
       </c>
       <c r="B662" t="n">
-        <v>6.1541111</v>
+        <v>65.27</v>
       </c>
       <c r="C662" t="n">
         <v>98.56999999999999</v>
@@ -15674,7 +15674,7 @@
         <v>2.03</v>
       </c>
       <c r="B663" t="n">
-        <v>6.1541111</v>
+        <v>85.37</v>
       </c>
       <c r="C663" t="n">
         <v>127.05</v>
@@ -15697,7 +15697,7 @@
         <v>1.04</v>
       </c>
       <c r="B664" t="n">
-        <v>6.1541111</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="C664" t="n">
         <v>55.79</v>
@@ -15720,7 +15720,7 @@
         <v>3.05</v>
       </c>
       <c r="B665" t="n">
-        <v>6.1541111</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="C665" t="n">
         <v>164.25</v>
@@ -15743,7 +15743,7 @@
         <v>1.71</v>
       </c>
       <c r="B666" t="n">
-        <v>6.1541111</v>
+        <v>84.59</v>
       </c>
       <c r="C666" t="n">
         <v>155.07</v>
@@ -15766,7 +15766,7 @@
         <v>0.5</v>
       </c>
       <c r="B667" t="n">
-        <v>6.1541111</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="C667" t="n">
         <v>234</v>
@@ -15789,7 +15789,7 @@
         <v>0.5</v>
       </c>
       <c r="B668" t="n">
-        <v>6.1541111</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="C668" t="n">
         <v>166.32</v>
@@ -15812,7 +15812,7 @@
         <v>2.3</v>
       </c>
       <c r="B669" t="n">
-        <v>6.1541111</v>
+        <v>91.36</v>
       </c>
       <c r="C669" t="n">
         <v>128.13</v>
@@ -15835,7 +15835,7 @@
         <v>2.63</v>
       </c>
       <c r="B670" t="n">
-        <v>6.1541111</v>
+        <v>79.3</v>
       </c>
       <c r="C670" t="n">
         <v>176.57</v>
@@ -15858,7 +15858,7 @@
         <v>1.2</v>
       </c>
       <c r="B671" t="n">
-        <v>6.1541111</v>
+        <v>60.37</v>
       </c>
       <c r="C671" t="n">
         <v>103.23</v>
@@ -15881,7 +15881,7 @@
         <v>4.03</v>
       </c>
       <c r="B672" t="n">
-        <v>6.1541111</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="C672" t="n">
         <v>254.13</v>
@@ -15904,7 +15904,7 @@
         <v>1.74</v>
       </c>
       <c r="B673" t="n">
-        <v>6.1541111</v>
+        <v>88.84</v>
       </c>
       <c r="C673" t="n">
         <v>138.63</v>
@@ -15927,7 +15927,7 @@
         <v>4.04</v>
       </c>
       <c r="B674" t="n">
-        <v>6.1541111</v>
+        <v>77.01000000000001</v>
       </c>
       <c r="C674" t="n">
         <v>119.53</v>
@@ -15950,7 +15950,7 @@
         <v>1.69</v>
       </c>
       <c r="B675" t="n">
-        <v>6.1541111</v>
+        <v>69.77</v>
       </c>
       <c r="C675" t="n">
         <v>433.86</v>
@@ -15973,7 +15973,7 @@
         <v>4.22</v>
       </c>
       <c r="B676" t="n">
-        <v>6.1541111</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="C676" t="n">
         <v>110.4</v>
@@ -15996,7 +15996,7 @@
         <v>2.12</v>
       </c>
       <c r="B677" t="n">
-        <v>6.1541111</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="C677" t="n">
         <v>423.95</v>
@@ -16019,7 +16019,7 @@
         <v>3.44</v>
       </c>
       <c r="B678" t="n">
-        <v>6.1541111</v>
+        <v>110.01</v>
       </c>
       <c r="C678" t="n">
         <v>136.85</v>
@@ -16042,7 +16042,7 @@
         <v>1.12</v>
       </c>
       <c r="B679" t="n">
-        <v>6.1541111</v>
+        <v>90.61</v>
       </c>
       <c r="C679" t="n">
         <v>163.08</v>
@@ -16065,7 +16065,7 @@
         <v>2.47</v>
       </c>
       <c r="B680" t="n">
-        <v>6.1541111</v>
+        <v>90.22</v>
       </c>
       <c r="C680" t="n">
         <v>267.02</v>
@@ -16088,7 +16088,7 @@
         <v>1.25</v>
       </c>
       <c r="B681" t="n">
-        <v>6.1541111</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="C681" t="n">
         <v>122.46</v>
@@ -16111,7 +16111,7 @@
         <v>3.77</v>
       </c>
       <c r="B682" t="n">
-        <v>6.1541111</v>
+        <v>95.37</v>
       </c>
       <c r="C682" t="n">
         <v>108.23</v>
@@ -16134,7 +16134,7 @@
         <v>4.61</v>
       </c>
       <c r="B683" t="n">
-        <v>6.1541111</v>
+        <v>93.06999999999999</v>
       </c>
       <c r="C683" t="n">
         <v>251.14</v>
@@ -16157,7 +16157,7 @@
         <v>2.71</v>
       </c>
       <c r="B684" t="n">
-        <v>6.1541111</v>
+        <v>100.59</v>
       </c>
       <c r="C684" t="n">
         <v>221.74</v>
@@ -16180,7 +16180,7 @@
         <v>3.96</v>
       </c>
       <c r="B685" t="n">
-        <v>6.1541111</v>
+        <v>79.31999999999999</v>
       </c>
       <c r="C685" t="n">
         <v>124.2</v>
@@ -16203,7 +16203,7 @@
         <v>1.51</v>
       </c>
       <c r="B686" t="n">
-        <v>6.1541111</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="C686" t="n">
         <v>77.90000000000001</v>
@@ -16226,7 +16226,7 @@
         <v>2.41</v>
       </c>
       <c r="B687" t="n">
-        <v>6.1541111</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="C687" t="n">
         <v>186.88</v>
@@ -16249,7 +16249,7 @@
         <v>2.41</v>
       </c>
       <c r="B688" t="n">
-        <v>6.1541111</v>
+        <v>95.06</v>
       </c>
       <c r="C688" t="n">
         <v>120.09</v>
@@ -16272,7 +16272,7 @@
         <v>2.53</v>
       </c>
       <c r="B689" t="n">
-        <v>6.1541111</v>
+        <v>103.55</v>
       </c>
       <c r="C689" t="n">
         <v>157.13</v>
@@ -16295,7 +16295,7 @@
         <v>0.5</v>
       </c>
       <c r="B690" t="n">
-        <v>6.1541111</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="C690" t="n">
         <v>281.19</v>
@@ -16318,7 +16318,7 @@
         <v>1.46</v>
       </c>
       <c r="B691" t="n">
-        <v>6.1541111</v>
+        <v>80.47</v>
       </c>
       <c r="C691" t="n">
         <v>214.34</v>
@@ -16341,7 +16341,7 @@
         <v>3.59</v>
       </c>
       <c r="B692" t="n">
-        <v>6.1541111</v>
+        <v>89.34</v>
       </c>
       <c r="C692" t="n">
         <v>139.44</v>
@@ -16364,7 +16364,7 @@
         <v>3.48</v>
       </c>
       <c r="B693" t="n">
-        <v>6.1541111</v>
+        <v>82.62</v>
       </c>
       <c r="C693" t="n">
         <v>142.97</v>
@@ -16387,7 +16387,7 @@
         <v>2.74</v>
       </c>
       <c r="B694" t="n">
-        <v>6.1541111</v>
+        <v>97</v>
       </c>
       <c r="C694" t="n">
         <v>107.86</v>
@@ -16410,7 +16410,7 @@
         <v>3.89</v>
       </c>
       <c r="B695" t="n">
-        <v>6.1541111</v>
+        <v>60.37</v>
       </c>
       <c r="C695" t="n">
         <v>143.33</v>
@@ -16433,7 +16433,7 @@
         <v>0.96</v>
       </c>
       <c r="B696" t="n">
-        <v>6.1541111</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="C696" t="n">
         <v>159.37</v>
@@ -16456,7 +16456,7 @@
         <v>3.49</v>
       </c>
       <c r="B697" t="n">
-        <v>6.1541111</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="C697" t="n">
         <v>119.05</v>
@@ -16479,7 +16479,7 @@
         <v>3.25</v>
       </c>
       <c r="B698" t="n">
-        <v>6.1541111</v>
+        <v>60.37</v>
       </c>
       <c r="C698" t="n">
         <v>160.77</v>
@@ -16502,7 +16502,7 @@
         <v>0.78</v>
       </c>
       <c r="B699" t="n">
-        <v>6.1541111</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="C699" t="n">
         <v>111.34</v>
@@ -16525,7 +16525,7 @@
         <v>2.72</v>
       </c>
       <c r="B700" t="n">
-        <v>6.1541111</v>
+        <v>74.59</v>
       </c>
       <c r="C700" t="n">
         <v>237.39</v>
@@ -16548,7 +16548,7 @@
         <v>4.3</v>
       </c>
       <c r="B701" t="n">
-        <v>6.1541111</v>
+        <v>83.16</v>
       </c>
       <c r="C701" t="n">
         <v>132.42</v>
@@ -16571,7 +16571,7 @@
         <v>3.02</v>
       </c>
       <c r="B702" t="n">
-        <v>6.1541111</v>
+        <v>98.93000000000001</v>
       </c>
       <c r="C702" t="n">
         <v>40</v>
@@ -16594,7 +16594,7 @@
         <v>1.26</v>
       </c>
       <c r="B703" t="n">
-        <v>6.1541111</v>
+        <v>82.63</v>
       </c>
       <c r="C703" t="n">
         <v>255.19</v>
@@ -16617,7 +16617,7 @@
         <v>1.86</v>
       </c>
       <c r="B704" t="n">
-        <v>6.1541111</v>
+        <v>73.2</v>
       </c>
       <c r="C704" t="n">
         <v>151.01</v>
@@ -16640,7 +16640,7 @@
         <v>2.61</v>
       </c>
       <c r="B705" t="n">
-        <v>6.1541111</v>
+        <v>84.89</v>
       </c>
       <c r="C705" t="n">
         <v>146.34</v>
@@ -16663,7 +16663,7 @@
         <v>1.88</v>
       </c>
       <c r="B706" t="n">
-        <v>6.1541111</v>
+        <v>98.16</v>
       </c>
       <c r="C706" t="n">
         <v>94.8</v>
@@ -16686,7 +16686,7 @@
         <v>3.09</v>
       </c>
       <c r="B707" t="n">
-        <v>6.1541111</v>
+        <v>73.86</v>
       </c>
       <c r="C707" t="n">
         <v>180.49</v>
@@ -16709,7 +16709,7 @@
         <v>3.25</v>
       </c>
       <c r="B708" t="n">
-        <v>6.1541111</v>
+        <v>74.64</v>
       </c>
       <c r="C708" t="n">
         <v>254.77</v>
@@ -16732,7 +16732,7 @@
         <v>3.56</v>
       </c>
       <c r="B709" t="n">
-        <v>6.1541111</v>
+        <v>92.27</v>
       </c>
       <c r="C709" t="n">
         <v>269.69</v>
@@ -16755,7 +16755,7 @@
         <v>2.38</v>
       </c>
       <c r="B710" t="n">
-        <v>6.1541111</v>
+        <v>82.91</v>
       </c>
       <c r="C710" t="n">
         <v>55.98</v>
@@ -16778,7 +16778,7 @@
         <v>2.42</v>
       </c>
       <c r="B711" t="n">
-        <v>6.1541111</v>
+        <v>93.34</v>
       </c>
       <c r="C711" t="n">
         <v>201.23</v>
@@ -16801,7 +16801,7 @@
         <v>2.94</v>
       </c>
       <c r="B712" t="n">
-        <v>6.1541111</v>
+        <v>85.42</v>
       </c>
       <c r="C712" t="n">
         <v>51.14</v>
@@ -16824,7 +16824,7 @@
         <v>3.17</v>
       </c>
       <c r="B713" t="n">
-        <v>6.1541111</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="C713" t="n">
         <v>170.12</v>
@@ -16847,7 +16847,7 @@
         <v>1.14</v>
       </c>
       <c r="B714" t="n">
-        <v>6.1541111</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="C714" t="n">
         <v>49.63</v>
@@ -16870,7 +16870,7 @@
         <v>2.8</v>
       </c>
       <c r="B715" t="n">
-        <v>6.1541111</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="C715" t="n">
         <v>331.37</v>
@@ -16893,7 +16893,7 @@
         <v>2.26</v>
       </c>
       <c r="B716" t="n">
-        <v>6.1541111</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="C716" t="n">
         <v>161.52</v>
@@ -16916,7 +16916,7 @@
         <v>5</v>
       </c>
       <c r="B717" t="n">
-        <v>6.1541111</v>
+        <v>70.98</v>
       </c>
       <c r="C717" t="n">
         <v>128.75</v>
@@ -16939,7 +16939,7 @@
         <v>2.86</v>
       </c>
       <c r="B718" t="n">
-        <v>6.1541111</v>
+        <v>66.81</v>
       </c>
       <c r="C718" t="n">
         <v>154.35</v>
@@ -16962,7 +16962,7 @@
         <v>3.13</v>
       </c>
       <c r="B719" t="n">
-        <v>6.1541111</v>
+        <v>93.8</v>
       </c>
       <c r="C719" t="n">
         <v>159.47</v>
@@ -16985,7 +16985,7 @@
         <v>3.68</v>
       </c>
       <c r="B720" t="n">
-        <v>6.1541111</v>
+        <v>81.36</v>
       </c>
       <c r="C720" t="n">
         <v>139.99</v>
@@ -17008,7 +17008,7 @@
         <v>3.27</v>
       </c>
       <c r="B721" t="n">
-        <v>6.1541111</v>
+        <v>73.3</v>
       </c>
       <c r="C721" t="n">
         <v>53.37</v>
@@ -17031,7 +17031,7 @@
         <v>0.95</v>
       </c>
       <c r="B722" t="n">
-        <v>6.1541111</v>
+        <v>84.42</v>
       </c>
       <c r="C722" t="n">
         <v>45.46</v>
@@ -17054,7 +17054,7 @@
         <v>2.57</v>
       </c>
       <c r="B723" t="n">
-        <v>6.1541111</v>
+        <v>99.11</v>
       </c>
       <c r="C723" t="n">
         <v>118.89</v>
@@ -17077,7 +17077,7 @@
         <v>2.28</v>
       </c>
       <c r="B724" t="n">
-        <v>6.1541111</v>
+        <v>60.37</v>
       </c>
       <c r="C724" t="n">
         <v>394.75</v>
@@ -17100,7 +17100,7 @@
         <v>3.75</v>
       </c>
       <c r="B725" t="n">
-        <v>6.1541111</v>
+        <v>67.61</v>
       </c>
       <c r="C725" t="n">
         <v>151.36</v>
@@ -17123,7 +17123,7 @@
         <v>3.85</v>
       </c>
       <c r="B726" t="n">
-        <v>6.1541111</v>
+        <v>74.5</v>
       </c>
       <c r="C726" t="n">
         <v>43.09</v>
@@ -17146,7 +17146,7 @@
         <v>3.49</v>
       </c>
       <c r="B727" t="n">
-        <v>6.1541111</v>
+        <v>103.11</v>
       </c>
       <c r="C727" t="n">
         <v>283.58</v>
@@ -17169,7 +17169,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="B728" t="n">
-        <v>6.1541111</v>
+        <v>88.95999999999999</v>
       </c>
       <c r="C728" t="n">
         <v>83.02</v>
@@ -17192,7 +17192,7 @@
         <v>3.84</v>
       </c>
       <c r="B729" t="n">
-        <v>6.1541111</v>
+        <v>94.78</v>
       </c>
       <c r="C729" t="n">
         <v>195.61</v>
@@ -17215,7 +17215,7 @@
         <v>1.46</v>
       </c>
       <c r="B730" t="n">
-        <v>6.1541111</v>
+        <v>71.89</v>
       </c>
       <c r="C730" t="n">
         <v>177.68</v>
@@ -17238,7 +17238,7 @@
         <v>0.55</v>
       </c>
       <c r="B731" t="n">
-        <v>6.1541111</v>
+        <v>72.14</v>
       </c>
       <c r="C731" t="n">
         <v>154.85</v>
@@ -17261,7 +17261,7 @@
         <v>1.66</v>
       </c>
       <c r="B732" t="n">
-        <v>6.1541111</v>
+        <v>90.95</v>
       </c>
       <c r="C732" t="n">
         <v>59.59</v>
@@ -17284,7 +17284,7 @@
         <v>3.42</v>
       </c>
       <c r="B733" t="n">
-        <v>6.1541111</v>
+        <v>86.27</v>
       </c>
       <c r="C733" t="n">
         <v>183</v>
@@ -17307,7 +17307,7 @@
         <v>4.35</v>
       </c>
       <c r="B734" t="n">
-        <v>6.1541111</v>
+        <v>92.16</v>
       </c>
       <c r="C734" t="n">
         <v>204.34</v>
@@ -17330,7 +17330,7 @@
         <v>0.99</v>
       </c>
       <c r="B735" t="n">
-        <v>6.1541111</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="C735" t="n">
         <v>112.67</v>
@@ -17353,7 +17353,7 @@
         <v>3.97</v>
       </c>
       <c r="B736" t="n">
-        <v>6.1541111</v>
+        <v>88.91</v>
       </c>
       <c r="C736" t="n">
         <v>227.14</v>
@@ -17376,7 +17376,7 @@
         <v>2.37</v>
       </c>
       <c r="B737" t="n">
-        <v>6.1541111</v>
+        <v>87.47</v>
       </c>
       <c r="C737" t="n">
         <v>189.56</v>
@@ -17399,7 +17399,7 @@
         <v>0.74</v>
       </c>
       <c r="B738" t="n">
-        <v>6.1541111</v>
+        <v>94.91</v>
       </c>
       <c r="C738" t="n">
         <v>83.29000000000001</v>
@@ -17422,7 +17422,7 @@
         <v>1.68</v>
       </c>
       <c r="B739" t="n">
-        <v>6.1541111</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="C739" t="n">
         <v>178.74</v>
@@ -17445,7 +17445,7 @@
         <v>1.22</v>
       </c>
       <c r="B740" t="n">
-        <v>6.1541111</v>
+        <v>66.13</v>
       </c>
       <c r="C740" t="n">
         <v>109.25</v>
@@ -17468,7 +17468,7 @@
         <v>1.87</v>
       </c>
       <c r="B741" t="n">
-        <v>6.1541111</v>
+        <v>60.37</v>
       </c>
       <c r="C741" t="n">
         <v>307.38</v>
@@ -17491,7 +17491,7 @@
         <v>1.5</v>
       </c>
       <c r="B742" t="n">
-        <v>6.1541111</v>
+        <v>97.59</v>
       </c>
       <c r="C742" t="n">
         <v>54.15</v>
@@ -17514,7 +17514,7 @@
         <v>1.09</v>
       </c>
       <c r="B743" t="n">
-        <v>6.1541111</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="C743" t="n">
         <v>259.99</v>
@@ -17537,7 +17537,7 @@
         <v>0.5</v>
       </c>
       <c r="B744" t="n">
-        <v>6.1541111</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="C744" t="n">
         <v>126.94</v>
@@ -17560,7 +17560,7 @@
         <v>2.46</v>
       </c>
       <c r="B745" t="n">
-        <v>6.1541111</v>
+        <v>63.25</v>
       </c>
       <c r="C745" t="n">
         <v>80.73999999999999</v>
@@ -17583,7 +17583,7 @@
         <v>1.02</v>
       </c>
       <c r="B746" t="n">
-        <v>6.1541111</v>
+        <v>86.76000000000001</v>
       </c>
       <c r="C746" t="n">
         <v>91.94</v>
@@ -17606,7 +17606,7 @@
         <v>1.45</v>
       </c>
       <c r="B747" t="n">
-        <v>6.1541111</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="C747" t="n">
         <v>153.49</v>
@@ -17629,7 +17629,7 @@
         <v>0.58</v>
       </c>
       <c r="B748" t="n">
-        <v>6.1541111</v>
+        <v>107.14</v>
       </c>
       <c r="C748" t="n">
         <v>113.95</v>
@@ -17652,7 +17652,7 @@
         <v>2.1</v>
       </c>
       <c r="B749" t="n">
-        <v>6.1541111</v>
+        <v>91.77</v>
       </c>
       <c r="C749" t="n">
         <v>265.16</v>
@@ -17675,7 +17675,7 @@
         <v>3.04</v>
       </c>
       <c r="B750" t="n">
-        <v>6.1541111</v>
+        <v>81.11</v>
       </c>
       <c r="C750" t="n">
         <v>95.39</v>
@@ -17698,7 +17698,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B751" t="n">
-        <v>6.1541111</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="C751" t="n">
         <v>74.09999999999999</v>
@@ -17721,7 +17721,7 @@
         <v>3.02</v>
       </c>
       <c r="B752" t="n">
-        <v>6.1541111</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="C752" t="n">
         <v>317.49</v>
@@ -17744,7 +17744,7 @@
         <v>2.97</v>
       </c>
       <c r="B753" t="n">
-        <v>6.1541111</v>
+        <v>81.98</v>
       </c>
       <c r="C753" t="n">
         <v>195.4</v>
@@ -17767,7 +17767,7 @@
         <v>1.05</v>
       </c>
       <c r="B754" t="n">
-        <v>6.1541111</v>
+        <v>73.39</v>
       </c>
       <c r="C754" t="n">
         <v>156.77</v>
@@ -17790,7 +17790,7 @@
         <v>3.03</v>
       </c>
       <c r="B755" t="n">
-        <v>6.1541111</v>
+        <v>110.01</v>
       </c>
       <c r="C755" t="n">
         <v>166.71</v>
@@ -17813,7 +17813,7 @@
         <v>0.93</v>
       </c>
       <c r="B756" t="n">
-        <v>6.1541111</v>
+        <v>106.99</v>
       </c>
       <c r="C756" t="n">
         <v>176.08</v>
@@ -17836,7 +17836,7 @@
         <v>3.89</v>
       </c>
       <c r="B757" t="n">
-        <v>6.1541111</v>
+        <v>99.2</v>
       </c>
       <c r="C757" t="n">
         <v>204.63</v>
@@ -17859,7 +17859,7 @@
         <v>5</v>
       </c>
       <c r="B758" t="n">
-        <v>6.1541111</v>
+        <v>74.52</v>
       </c>
       <c r="C758" t="n">
         <v>198.89</v>
@@ -17882,7 +17882,7 @@
         <v>0.71</v>
       </c>
       <c r="B759" t="n">
-        <v>6.1541111</v>
+        <v>95.83</v>
       </c>
       <c r="C759" t="n">
         <v>215.18</v>
@@ -17905,7 +17905,7 @@
         <v>2.59</v>
       </c>
       <c r="B760" t="n">
-        <v>6.1541111</v>
+        <v>93.25</v>
       </c>
       <c r="C760" t="n">
         <v>201.17</v>
@@ -17928,7 +17928,7 @@
         <v>1.25</v>
       </c>
       <c r="B761" t="n">
-        <v>6.1541111</v>
+        <v>90.88</v>
       </c>
       <c r="C761" t="n">
         <v>152.45</v>
@@ -17951,7 +17951,7 @@
         <v>3.53</v>
       </c>
       <c r="B762" t="n">
-        <v>6.1541111</v>
+        <v>100.57</v>
       </c>
       <c r="C762" t="n">
         <v>163.26</v>
@@ -17974,7 +17974,7 @@
         <v>1.72</v>
       </c>
       <c r="B763" t="n">
-        <v>6.1541111</v>
+        <v>93.2</v>
       </c>
       <c r="C763" t="n">
         <v>86.37</v>
@@ -17997,7 +17997,7 @@
         <v>3.42</v>
       </c>
       <c r="B764" t="n">
-        <v>6.1541111</v>
+        <v>94.45</v>
       </c>
       <c r="C764" t="n">
         <v>173.99</v>
@@ -18020,7 +18020,7 @@
         <v>1.22</v>
       </c>
       <c r="B765" t="n">
-        <v>6.1541111</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="C765" t="n">
         <v>92.58</v>
@@ -18043,7 +18043,7 @@
         <v>1.75</v>
       </c>
       <c r="B766" t="n">
-        <v>6.1541111</v>
+        <v>89.66</v>
       </c>
       <c r="C766" t="n">
         <v>194.91</v>
@@ -18066,7 +18066,7 @@
         <v>1.35</v>
       </c>
       <c r="B767" t="n">
-        <v>6.1541111</v>
+        <v>64.17</v>
       </c>
       <c r="C767" t="n">
         <v>87.45</v>
@@ -18089,7 +18089,7 @@
         <v>1.55</v>
       </c>
       <c r="B768" t="n">
-        <v>6.1541111</v>
+        <v>86.58</v>
       </c>
       <c r="C768" t="n">
         <v>408.11</v>
@@ -18112,7 +18112,7 @@
         <v>3.79</v>
       </c>
       <c r="B769" t="n">
-        <v>6.1541111</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="C769" t="n">
         <v>193.63</v>
@@ -18135,7 +18135,7 @@
         <v>1.6</v>
       </c>
       <c r="B770" t="n">
-        <v>6.1541111</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="C770" t="n">
         <v>130.72</v>
@@ -18158,7 +18158,7 @@
         <v>1.46</v>
       </c>
       <c r="B771" t="n">
-        <v>6.1541111</v>
+        <v>105.75</v>
       </c>
       <c r="C771" t="n">
         <v>198.82</v>
@@ -18181,7 +18181,7 @@
         <v>1.89</v>
       </c>
       <c r="B772" t="n">
-        <v>6.1541111</v>
+        <v>106.32</v>
       </c>
       <c r="C772" t="n">
         <v>134.56</v>
@@ -18204,7 +18204,7 @@
         <v>2.07</v>
       </c>
       <c r="B773" t="n">
-        <v>6.1541111</v>
+        <v>101.88</v>
       </c>
       <c r="C773" t="n">
         <v>201.81</v>
@@ -18227,7 +18227,7 @@
         <v>2.18</v>
       </c>
       <c r="B774" t="n">
-        <v>6.1541111</v>
+        <v>88.63</v>
       </c>
       <c r="C774" t="n">
         <v>237.36</v>
@@ -18250,7 +18250,7 @@
         <v>1.94</v>
       </c>
       <c r="B775" t="n">
-        <v>6.1541111</v>
+        <v>101.78</v>
       </c>
       <c r="C775" t="n">
         <v>161.37</v>
@@ -18273,7 +18273,7 @@
         <v>2.99</v>
       </c>
       <c r="B776" t="n">
-        <v>6.1541111</v>
+        <v>85.72</v>
       </c>
       <c r="C776" t="n">
         <v>57.11</v>
@@ -18296,7 +18296,7 @@
         <v>3.79</v>
       </c>
       <c r="B777" t="n">
-        <v>6.1541111</v>
+        <v>88.01000000000001</v>
       </c>
       <c r="C777" t="n">
         <v>55.17</v>
@@ -18319,7 +18319,7 @@
         <v>2.5</v>
       </c>
       <c r="B778" t="n">
-        <v>6.1541111</v>
+        <v>72.45</v>
       </c>
       <c r="C778" t="n">
         <v>56.11</v>
@@ -18342,7 +18342,7 @@
         <v>1.98</v>
       </c>
       <c r="B779" t="n">
-        <v>6.1541111</v>
+        <v>90.34</v>
       </c>
       <c r="C779" t="n">
         <v>118.37</v>
@@ -18365,7 +18365,7 @@
         <v>2</v>
       </c>
       <c r="B780" t="n">
-        <v>6.1541111</v>
+        <v>86.3</v>
       </c>
       <c r="C780" t="n">
         <v>210.44</v>
@@ -18388,7 +18388,7 @@
         <v>1.95</v>
       </c>
       <c r="B781" t="n">
-        <v>6.1541111</v>
+        <v>69.94</v>
       </c>
       <c r="C781" t="n">
         <v>133.77</v>
@@ -18411,7 +18411,7 @@
         <v>2.58</v>
       </c>
       <c r="B782" t="n">
-        <v>6.1541111</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="C782" t="n">
         <v>156.65</v>
@@ -18434,7 +18434,7 @@
         <v>0.51</v>
       </c>
       <c r="B783" t="n">
-        <v>6.1541111</v>
+        <v>84.62</v>
       </c>
       <c r="C783" t="n">
         <v>219.12</v>
@@ -18457,7 +18457,7 @@
         <v>0.75</v>
       </c>
       <c r="B784" t="n">
-        <v>6.1541111</v>
+        <v>107.14</v>
       </c>
       <c r="C784" t="n">
         <v>456.59</v>
@@ -18480,7 +18480,7 @@
         <v>3.32</v>
       </c>
       <c r="B785" t="n">
-        <v>6.1541111</v>
+        <v>96.3</v>
       </c>
       <c r="C785" t="n">
         <v>400.56</v>
@@ -18503,7 +18503,7 @@
         <v>3.55</v>
       </c>
       <c r="B786" t="n">
-        <v>6.1541111</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="C786" t="n">
         <v>163.77</v>
@@ -18526,7 +18526,7 @@
         <v>2.57</v>
       </c>
       <c r="B787" t="n">
-        <v>6.1541111</v>
+        <v>88.56</v>
       </c>
       <c r="C787" t="n">
         <v>175.74</v>
@@ -18549,7 +18549,7 @@
         <v>2.42</v>
       </c>
       <c r="B788" t="n">
-        <v>6.1541111</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="C788" t="n">
         <v>101.71</v>
@@ -18572,7 +18572,7 @@
         <v>1.42</v>
       </c>
       <c r="B789" t="n">
-        <v>6.1541111</v>
+        <v>83.14</v>
       </c>
       <c r="C789" t="n">
         <v>166.54</v>
@@ -18595,7 +18595,7 @@
         <v>3.24</v>
       </c>
       <c r="B790" t="n">
-        <v>6.1541111</v>
+        <v>72.58</v>
       </c>
       <c r="C790" t="n">
         <v>168.09</v>
@@ -18618,7 +18618,7 @@
         <v>2.26</v>
       </c>
       <c r="B791" t="n">
-        <v>6.1541111</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="C791" t="n">
         <v>183.12</v>
@@ -18641,7 +18641,7 @@
         <v>3.12</v>
       </c>
       <c r="B792" t="n">
-        <v>6.1541111</v>
+        <v>76.62</v>
       </c>
       <c r="C792" t="n">
         <v>238.04</v>
@@ -18664,7 +18664,7 @@
         <v>2.23</v>
       </c>
       <c r="B793" t="n">
-        <v>6.1541111</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="C793" t="n">
         <v>192.66</v>
@@ -18687,7 +18687,7 @@
         <v>3.32</v>
       </c>
       <c r="B794" t="n">
-        <v>6.1541111</v>
+        <v>91.70999999999999</v>
       </c>
       <c r="C794" t="n">
         <v>470</v>
@@ -18710,7 +18710,7 @@
         <v>0.84</v>
       </c>
       <c r="B795" t="n">
-        <v>6.1541111</v>
+        <v>90.27</v>
       </c>
       <c r="C795" t="n">
         <v>121.07</v>
@@ -18733,7 +18733,7 @@
         <v>1.22</v>
       </c>
       <c r="B796" t="n">
-        <v>6.1541111</v>
+        <v>64.13</v>
       </c>
       <c r="C796" t="n">
         <v>217.29</v>
@@ -18756,7 +18756,7 @@
         <v>2.3</v>
       </c>
       <c r="B797" t="n">
-        <v>6.1541111</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="C797" t="n">
         <v>237.97</v>
@@ -18779,7 +18779,7 @@
         <v>1.45</v>
       </c>
       <c r="B798" t="n">
-        <v>6.1541111</v>
+        <v>97.52</v>
       </c>
       <c r="C798" t="n">
         <v>199.03</v>
@@ -18802,7 +18802,7 @@
         <v>2.24</v>
       </c>
       <c r="B799" t="n">
-        <v>6.1541111</v>
+        <v>98.28</v>
       </c>
       <c r="C799" t="n">
         <v>211.8</v>
